--- a/Versão5/CROM/Ontologia_CROMA.xlsx
+++ b/Versão5/CROM/Ontologia_CROMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CROM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168BE13B-2C01-405C-982C-623A4DD7C805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33761365-1C4D-4F3C-BEE8-6E3DDED8E76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -2287,12 +2287,63 @@
     <t xml:space="preserve">red exactly 1  , green exactly 1  , blue exactly 1  , alfa exactly 1 </t>
   </si>
   <si>
+    <t>Red and Green and  Blue</t>
+  </si>
+  <si>
+    <t>Red and Green and  Blue and Alfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyan and Magenta and  Yellow </t>
+  </si>
+  <si>
+    <t>Cyan and Magenta and  Yellow and Black</t>
+  </si>
+  <si>
+    <t>Canal.de.Cor</t>
+  </si>
+  <si>
+    <t>Cor.RGB</t>
+  </si>
+  <si>
+    <t>Cor.CMY</t>
+  </si>
+  <si>
+    <t>Cor.RGBA</t>
+  </si>
+  <si>
+    <t>Cor.CMYB</t>
+  </si>
+  <si>
+    <t>"É uma cor RGB"</t>
+  </si>
+  <si>
+    <t>"É uma cor RGBA"</t>
+  </si>
+  <si>
+    <t>"É uma cor CMY"</t>
+  </si>
+  <si>
+    <t>"É uma cor CMYB"</t>
+  </si>
+  <si>
+    <t>"É uma cor formada pelos canais CMY"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cyan min 0 , cyan max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow min 0 ,  yellow max 255  </t>
+  </si>
+  <si>
     <t xml:space="preserve">magenta min 0   ,  magenta max 255  </t>
   </si>
   <si>
     <t xml:space="preserve">black min 0   ,  black max 255  </t>
   </si>
   <si>
+    <t xml:space="preserve">red min 0  ,  red max 255  </t>
+  </si>
+  <si>
     <t xml:space="preserve">green min 0   ,  green max 255  </t>
   </si>
   <si>
@@ -2300,57 +2351,6 @@
   </si>
   <si>
     <t xml:space="preserve">alfa min 0   ,  alfa max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">cyan min 0 ,  cyan max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow min 0 ,  yellow max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">red min 0  ,  red max 255  </t>
-  </si>
-  <si>
-    <t>Red and Green and  Blue</t>
-  </si>
-  <si>
-    <t>Red and Green and  Blue and Alfa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyan and Magenta and  Yellow </t>
-  </si>
-  <si>
-    <t>Cyan and Magenta and  Yellow and Black</t>
-  </si>
-  <si>
-    <t>Canal.de.Cor</t>
-  </si>
-  <si>
-    <t>Cor.RGB</t>
-  </si>
-  <si>
-    <t>Cor.CMY</t>
-  </si>
-  <si>
-    <t>Cor.RGBA</t>
-  </si>
-  <si>
-    <t>Cor.CMYB</t>
-  </si>
-  <si>
-    <t>"É uma cor RGB"</t>
-  </si>
-  <si>
-    <t>"É uma cor RGBA"</t>
-  </si>
-  <si>
-    <t>"É uma cor CMY"</t>
-  </si>
-  <si>
-    <t>"É uma cor CMYB"</t>
-  </si>
-  <si>
-    <t>"É uma cor formada pelos canais CMY"</t>
   </si>
 </sst>
 </file>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46151.357984374998</v>
+        <v>46152.413960763886</v>
       </c>
       <c r="C18" s="64" t="s">
         <v>265</v>
@@ -4342,7 +4342,7 @@
         <v>117</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>132</v>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="79" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="L7" s="74" t="str">
         <f>_xlfn.CONCAT(C7)</f>
@@ -4435,7 +4435,7 @@
         <v>117</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F8" s="28" t="s">
         <v>131</v>
@@ -4453,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="79" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="L8" s="74" t="str">
         <f>_xlfn.CONCAT(C8)</f>
@@ -4528,7 +4528,7 @@
         <v>117</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>133</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="79" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="L9" s="74" t="str">
         <f>_xlfn.CONCAT(C9)</f>
@@ -4621,7 +4621,7 @@
         <v>117</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F10" s="28" t="s">
         <v>134</v>
@@ -4639,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="79" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="L10" s="74" t="str">
         <f t="shared" ref="L10:L24" si="10">_xlfn.CONCAT(C10)</f>
@@ -4714,7 +4714,7 @@
         <v>117</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>94</v>
@@ -4732,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="79" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="L11" s="74" t="str">
         <f>_xlfn.CONCAT(C11)</f>
@@ -4807,7 +4807,7 @@
         <v>117</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F12" s="28" t="s">
         <v>95</v>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="79" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="L12" s="74" t="str">
         <f>_xlfn.CONCAT(C12)</f>
@@ -4900,7 +4900,7 @@
         <v>117</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>96</v>
@@ -4918,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="L13" s="74" t="str">
         <f>_xlfn.CONCAT(C13)</f>
@@ -4993,7 +4993,7 @@
         <v>117</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F14" s="28" t="s">
         <v>97</v>
@@ -5011,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="79" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="L14" s="74" t="str">
         <f t="shared" ref="L14:L16" si="11">_xlfn.CONCAT(C14)</f>
@@ -5104,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="L15" s="77" t="str">
         <f t="shared" si="11"/>
@@ -5197,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="L16" s="77" t="str">
         <f t="shared" si="11"/>
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="L17" s="77" t="str">
         <f t="shared" si="10"/>
@@ -5383,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="L18" s="77" t="str">
         <f t="shared" si="10"/>
@@ -6424,13 +6424,13 @@
         <v>130</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H2" s="32" t="s">
         <v>130</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J2" s="60" t="s">
         <v>1</v>
@@ -6496,13 +6496,13 @@
         <v>130</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>130</v>
       </c>
       <c r="I3" s="35" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J3" s="60" t="s">
         <v>1</v>
@@ -6568,13 +6568,13 @@
         <v>130</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H4" s="32" t="s">
         <v>130</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J4" s="60" t="s">
         <v>1</v>
@@ -6640,13 +6640,13 @@
         <v>130</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>130</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J5" s="60" t="s">
         <v>1</v>
@@ -6712,7 +6712,7 @@
         <v>130</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H6" s="60" t="s">
         <v>1</v>
@@ -6784,7 +6784,7 @@
         <v>130</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H7" s="60" t="s">
         <v>1</v>
@@ -6856,7 +6856,7 @@
         <v>130</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H8" s="60" t="s">
         <v>1</v>
@@ -6928,7 +6928,7 @@
         <v>130</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H9" s="60" t="s">
         <v>1</v>
@@ -7000,7 +7000,7 @@
         <v>130</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H10" s="60" t="s">
         <v>1</v>
@@ -7072,7 +7072,7 @@
         <v>130</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H11" s="60" t="s">
         <v>1</v>
@@ -7144,7 +7144,7 @@
         <v>130</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H12" s="60" t="s">
         <v>1</v>
@@ -7216,7 +7216,7 @@
         <v>130</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H13" s="60" t="s">
         <v>1</v>
@@ -7288,7 +7288,7 @@
         <v>130</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="H14" s="60" t="s">
         <v>1</v>
@@ -7306,7 +7306,7 @@
         <v>151</v>
       </c>
       <c r="M14" s="50" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N14" s="47" t="s">
         <v>143</v>
@@ -7360,7 +7360,7 @@
         <v>130</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="H15" s="60" t="s">
         <v>1</v>
@@ -7378,7 +7378,7 @@
         <v>151</v>
       </c>
       <c r="M15" s="50" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N15" s="47" t="s">
         <v>143</v>
@@ -7561,7 +7561,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>138</v>
@@ -7594,7 +7594,7 @@
         <v>151</v>
       </c>
       <c r="M18" s="50" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="N18" s="55" t="s">
         <v>1</v>
@@ -7633,7 +7633,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>136</v>
@@ -7666,7 +7666,7 @@
         <v>151</v>
       </c>
       <c r="M19" s="50" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="N19" s="55" t="s">
         <v>1</v>
@@ -7705,7 +7705,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>137</v>
@@ -7738,7 +7738,7 @@
         <v>151</v>
       </c>
       <c r="M20" s="50" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="N20" s="55" t="s">
         <v>1</v>
@@ -7777,7 +7777,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>135</v>
@@ -7810,7 +7810,7 @@
         <v>151</v>
       </c>
       <c r="M21" s="50" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="N21" s="55" t="s">
         <v>1</v>
@@ -10763,7 +10763,7 @@
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A18:B18 A19:XFD19 A20:B21 A22:XFD1048576 A1:XFD17">
+  <conditionalFormatting sqref="A1:XFD17 A18:B18 A19:XFD19 A20:B21 A22:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>

--- a/Versão5/CROM/Ontologia_CROMA.xlsx
+++ b/Versão5/CROM/Ontologia_CROMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CROM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33761365-1C4D-4F3C-BEE8-6E3DDED8E76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D024D10F-9464-4276-A4FF-B2F10CE00F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -1579,15 +1579,6 @@
     <t>Equivalente a</t>
   </si>
   <si>
-    <t>red</t>
-  </si>
-  <si>
-    <t>green</t>
-  </si>
-  <si>
-    <t>blue</t>
-  </si>
-  <si>
     <t>Cinza.Claro</t>
   </si>
   <si>
@@ -1597,9 +1588,6 @@
     <t>Cinza.Escuro</t>
   </si>
   <si>
-    <t>alfa</t>
-  </si>
-  <si>
     <t>Canal.R</t>
   </si>
   <si>
@@ -1627,9 +1615,6 @@
     <t>Puro.B</t>
   </si>
   <si>
-    <t>rgb</t>
-  </si>
-  <si>
     <t>Pantone</t>
   </si>
   <si>
@@ -1684,18 +1669,9 @@
     <t>Paleta.DNIT</t>
   </si>
   <si>
-    <t>magenta</t>
-  </si>
-  <si>
-    <t>yellow</t>
-  </si>
-  <si>
     <t>Paleta.Pantone</t>
   </si>
   <si>
-    <t>cyan</t>
-  </si>
-  <si>
     <t>nome</t>
   </si>
   <si>
@@ -1744,9 +1720,6 @@
     <t>Cor.Adi.02</t>
   </si>
   <si>
-    <t>cmy</t>
-  </si>
-  <si>
     <t>Munsell</t>
   </si>
   <si>
@@ -2329,28 +2302,55 @@
     <t>"É uma cor formada pelos canais CMY"</t>
   </si>
   <si>
-    <t xml:space="preserve">cyan min 0 , cyan max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow min 0 ,  yellow max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">magenta min 0   ,  magenta max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">black min 0   ,  black max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">red min 0  ,  red max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">green min 0   ,  green max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue min 0   ,  blue max 255  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">alfa min 0   ,  alfa max 255  </t>
+    <t xml:space="preserve">canal.alfa min 0   ,  canal.alfa max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.green min 0   ,  canal.green max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.black min 0   ,  canal.black max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.red min 0  ,  canal.red max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.cyan min 0 , canal.cyan max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.magenta min 0   ,  canal.magenta max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.yellow min 0 ,  canal.yellow max 255  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">canal.blue min 0   ,  canal.blue max 255  </t>
+  </si>
+  <si>
+    <t>canal.red</t>
+  </si>
+  <si>
+    <t>canal.green</t>
+  </si>
+  <si>
+    <t>canal.blue</t>
+  </si>
+  <si>
+    <t>canal.alfa</t>
+  </si>
+  <si>
+    <t>canal.cyan</t>
+  </si>
+  <si>
+    <t>canal.magenta</t>
+  </si>
+  <si>
+    <t>canal.yellow</t>
+  </si>
+  <si>
+    <t>cor.rgb</t>
+  </si>
+  <si>
+    <t>cor.cmy</t>
   </si>
 </sst>
 </file>
@@ -3451,15 +3451,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3467,10 +3467,10 @@
         <v>50</v>
       </c>
       <c r="C1" s="52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3478,10 +3478,10 @@
         <v>76</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3489,10 +3489,10 @@
         <v>99</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3500,10 +3500,10 @@
         <v>62</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3512,10 +3512,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3524,10 +3524,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3535,21 +3535,21 @@
         <v>63</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3557,10 +3557,10 @@
         <v>65</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3568,10 +3568,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3579,10 +3579,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3590,10 +3590,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3601,10 +3601,10 @@
         <v>38</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3612,10 +3612,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3623,10 +3623,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3634,10 +3634,10 @@
         <v>38</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3645,57 +3645,57 @@
         <v>100</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46152.413960763886</v>
+        <v>46191.452614699076</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="43" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="43" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B20" s="66" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="43" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B21" s="66" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3703,10 +3703,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3714,10 +3714,10 @@
         <v>38</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3725,10 +3725,10 @@
         <v>101</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3736,19 +3736,19 @@
         <v>102</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of chromatic elements</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3759,33 +3759,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AA24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" customWidth="1"/>
-    <col min="2" max="2" width="5.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="7.15234375" customWidth="1"/>
-    <col min="7" max="9" width="6.4609375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.3828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47.3046875" customWidth="1"/>
-    <col min="12" max="14" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.28515625" customWidth="1"/>
+    <col min="12" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="101.53515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="98.3828125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="101.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="98.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.15234375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.84375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.07421875" customWidth="1"/>
-    <col min="25" max="25" width="5.07421875" customWidth="1"/>
-    <col min="26" max="26" width="5.765625" customWidth="1"/>
-    <col min="27" max="27" width="79.3828125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" customWidth="1"/>
+    <col min="25" max="25" width="5.140625" customWidth="1"/>
+    <col min="26" max="26" width="5.7109375" customWidth="1"/>
+    <col min="27" max="27" width="79.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
@@ -3856,36 +3856,36 @@
         <v>0</v>
       </c>
       <c r="X1" s="25" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Y1" s="25" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z1" s="25" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA1" s="62" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="67">
         <v>2</v>
       </c>
       <c r="B2" s="68" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F2" s="69" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="G2" s="70" t="s">
         <v>1</v>
@@ -3919,10 +3919,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="63" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="Q2" s="63" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="R2" s="72" t="s">
         <v>1</v>
@@ -3960,24 +3960,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67">
         <v>3</v>
       </c>
       <c r="B3" s="68" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F3" s="69" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G3" s="70" t="s">
         <v>1</v>
@@ -4011,10 +4011,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="63" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="Q3" s="63" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="R3" s="72" t="s">
         <v>1</v>
@@ -4052,24 +4052,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="67">
         <v>4</v>
       </c>
       <c r="B4" s="68" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D4" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="69" t="s">
         <v>277</v>
-      </c>
-      <c r="E4" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>286</v>
       </c>
       <c r="G4" s="70" t="s">
         <v>1</v>
@@ -4103,10 +4103,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="63" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="Q4" s="63" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="R4" s="72" t="s">
         <v>1</v>
@@ -4144,24 +4144,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="67">
         <v>5</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="G5" s="70" t="s">
         <v>1</v>
@@ -4195,10 +4195,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="63" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="Q5" s="63" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="R5" s="72" t="s">
         <v>1</v>
@@ -4236,24 +4236,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="67">
         <v>6</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E6" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="69" t="s">
         <v>281</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>290</v>
       </c>
       <c r="G6" s="70" t="s">
         <v>1</v>
@@ -4287,10 +4287,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="63" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="Q6" s="63" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="R6" s="72" t="s">
         <v>1</v>
@@ -4328,7 +4328,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67">
         <v>7</v>
       </c>
@@ -4336,16 +4336,16 @@
         <v>93</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G7" s="70" t="s">
         <v>1</v>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="79" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L7" s="74" t="str">
         <f>_xlfn.CONCAT(C7)</f>
@@ -4379,7 +4379,7 @@
         <v>Cyan</v>
       </c>
       <c r="P7" s="74" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Q7" s="74" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -4421,7 +4421,7 @@
         <v>Amount of cyan color that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="67">
         <v>8</v>
       </c>
@@ -4429,16 +4429,16 @@
         <v>93</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G8" s="70" t="s">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="79" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="L8" s="74" t="str">
         <f>_xlfn.CONCAT(C8)</f>
@@ -4472,7 +4472,7 @@
         <v>Magenta</v>
       </c>
       <c r="P8" s="74" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="Q8" s="74" t="str">
         <f t="shared" ref="Q8:Q24" si="8">_xlfn.TRANSLATE(P8,"pt","es")</f>
@@ -4514,7 +4514,7 @@
         <v>Amount of magenta color that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="67">
         <v>9</v>
       </c>
@@ -4522,16 +4522,16 @@
         <v>93</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G9" s="70" t="s">
         <v>1</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="79" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L9" s="74" t="str">
         <f>_xlfn.CONCAT(C9)</f>
@@ -4565,7 +4565,7 @@
         <v>Yellow</v>
       </c>
       <c r="P9" s="74" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="Q9" s="74" t="str">
         <f t="shared" si="8"/>
@@ -4607,7 +4607,7 @@
         <v>Amount of yellow color between which can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67">
         <v>10</v>
       </c>
@@ -4615,16 +4615,16 @@
         <v>93</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G10" s="70" t="s">
         <v>1</v>
@@ -4639,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="79" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L10" s="74" t="str">
         <f t="shared" ref="L10:L24" si="10">_xlfn.CONCAT(C10)</f>
@@ -4658,7 +4658,7 @@
         <v>Black</v>
       </c>
       <c r="P10" s="74" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="Q10" s="74" t="str">
         <f t="shared" si="8"/>
@@ -4700,7 +4700,7 @@
         <v>Amount of black color between which can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
         <v>11</v>
       </c>
@@ -4708,13 +4708,13 @@
         <v>93</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>94</v>
@@ -4732,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="79" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="L11" s="74" t="str">
         <f>_xlfn.CONCAT(C11)</f>
@@ -4751,7 +4751,7 @@
         <v>Red</v>
       </c>
       <c r="P11" s="74" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="Q11" s="74" t="str">
         <f t="shared" si="8"/>
@@ -4793,7 +4793,7 @@
         <v>Amount of red color that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
         <v>12</v>
       </c>
@@ -4801,13 +4801,13 @@
         <v>93</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F12" s="28" t="s">
         <v>95</v>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="79" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="L12" s="74" t="str">
         <f>_xlfn.CONCAT(C12)</f>
@@ -4844,7 +4844,7 @@
         <v>Green</v>
       </c>
       <c r="P12" s="74" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="Q12" s="74" t="str">
         <f t="shared" si="8"/>
@@ -4886,7 +4886,7 @@
         <v>Amount of green color between that can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
         <v>13</v>
       </c>
@@ -4894,13 +4894,13 @@
         <v>93</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>96</v>
@@ -4918,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L13" s="74" t="str">
         <f>_xlfn.CONCAT(C13)</f>
@@ -4937,7 +4937,7 @@
         <v>Blue</v>
       </c>
       <c r="P13" s="74" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="Q13" s="74" t="str">
         <f t="shared" si="8"/>
@@ -4979,7 +4979,7 @@
         <v>Amount of blue color between that can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
         <v>14</v>
       </c>
@@ -4987,13 +4987,13 @@
         <v>93</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F14" s="28" t="s">
         <v>97</v>
@@ -5011,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="79" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="L14" s="74" t="str">
         <f t="shared" ref="L14:L16" si="11">_xlfn.CONCAT(C14)</f>
@@ -5030,7 +5030,7 @@
         <v>Alfa</v>
       </c>
       <c r="P14" s="74" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Q14" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5072,7 +5072,7 @@
         <v>Amount of transparency that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
         <v>15</v>
       </c>
@@ -5080,16 +5080,16 @@
         <v>93</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E15" s="45" t="s">
         <v>98</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G15" s="70" t="s">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L15" s="77" t="str">
         <f t="shared" si="11"/>
@@ -5123,7 +5123,7 @@
         <v>CMY</v>
       </c>
       <c r="P15" s="77" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="Q15" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5165,7 +5165,7 @@
         <v>Digital color composed of CMY channels.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67">
         <v>16</v>
       </c>
@@ -5173,16 +5173,16 @@
         <v>93</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D16" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E16" s="45" t="s">
         <v>98</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G16" s="70" t="s">
         <v>1</v>
@@ -5197,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="L16" s="77" t="str">
         <f t="shared" si="11"/>
@@ -5216,7 +5216,7 @@
         <v>CMYB</v>
       </c>
       <c r="P16" s="77" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="Q16" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5258,7 +5258,7 @@
         <v>Digital color composed of CMYB channels.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67">
         <v>17</v>
       </c>
@@ -5266,16 +5266,16 @@
         <v>93</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E17" s="45" t="s">
         <v>98</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G17" s="70" t="s">
         <v>1</v>
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="L17" s="77" t="str">
         <f t="shared" si="10"/>
@@ -5309,7 +5309,7 @@
         <v>RGB</v>
       </c>
       <c r="P17" s="77" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="Q17" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5351,7 +5351,7 @@
         <v>Digital color composed of RGB channels.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
         <v>18</v>
       </c>
@@ -5359,16 +5359,16 @@
         <v>93</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D18" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E18" s="45" t="s">
         <v>98</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G18" s="70" t="s">
         <v>1</v>
@@ -5383,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="L18" s="77" t="str">
         <f t="shared" si="10"/>
@@ -5402,7 +5402,7 @@
         <v>RGBA</v>
       </c>
       <c r="P18" s="77" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="Q18" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5444,7 +5444,7 @@
         <v>Digital color composed of RGBA channels. Channel A defines transparency.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
         <v>19</v>
       </c>
@@ -5452,16 +5452,16 @@
         <v>93</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D19" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G19" s="70" t="s">
         <v>1</v>
@@ -5495,7 +5495,7 @@
         <v>Hue</v>
       </c>
       <c r="P19" s="77" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="Q19" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5537,7 +5537,7 @@
         <v>Munsell Color System: Hue Parameter.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="67">
         <v>20</v>
       </c>
@@ -5545,16 +5545,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D20" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G20" s="70" t="s">
         <v>1</v>
@@ -5588,7 +5588,7 @@
         <v>Luminosidade</v>
       </c>
       <c r="P20" s="77" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="Q20" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5630,7 +5630,7 @@
         <v>Munsell color system: Luminosity parameter.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
         <v>21</v>
       </c>
@@ -5638,16 +5638,16 @@
         <v>93</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G21" s="70" t="s">
         <v>1</v>
@@ -5681,7 +5681,7 @@
         <v>Croma</v>
       </c>
       <c r="P21" s="77" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="Q21" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5723,7 +5723,7 @@
         <v>Munsell Color System: Parameter Chroma. It is the degree of distance of a color from the neutral color of the same value. A low chroma weakens the color. A high chroma for saturated, strong, or vivid color.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
         <v>22</v>
       </c>
@@ -5731,16 +5731,16 @@
         <v>93</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D22" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="G22" s="70" t="s">
         <v>1</v>
@@ -5774,7 +5774,7 @@
         <v>Cor.Munsell</v>
       </c>
       <c r="P22" s="77" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="Q22" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5816,7 +5816,7 @@
         <v>Munsell system-specific color.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
         <v>23</v>
       </c>
@@ -5824,16 +5824,16 @@
         <v>93</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D23" s="45" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G23" s="70" t="s">
         <v>1</v>
@@ -5867,7 +5867,7 @@
         <v xml:space="preserve">Cor.Pantone </v>
       </c>
       <c r="P23" s="77" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="Q23" s="74" t="str">
         <f t="shared" si="8"/>
@@ -5909,7 +5909,7 @@
         <v>Specific color from the Pantone catalog.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
         <v>24</v>
       </c>
@@ -5917,16 +5917,16 @@
         <v>93</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G24" s="70" t="s">
         <v>1</v>
@@ -5960,7 +5960,7 @@
         <v xml:space="preserve">Cor.Dnit </v>
       </c>
       <c r="P24" s="77" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="Q24" s="74" t="str">
         <f t="shared" si="8"/>
@@ -6046,15 +6046,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="41" t="s">
         <v>22</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="41">
         <v>2</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
         <v>3</v>
       </c>
@@ -6264,14 +6264,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38">
         <v>1</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -6306,34 +6306,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.53515625" customWidth="1"/>
-    <col min="2" max="2" width="8.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.3828125" customWidth="1"/>
-    <col min="4" max="4" width="9.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.15234375" customWidth="1"/>
-    <col min="7" max="7" width="6.765625" customWidth="1"/>
-    <col min="8" max="8" width="5.69140625" style="49" customWidth="1"/>
-    <col min="9" max="9" width="6.23046875" style="49" customWidth="1"/>
-    <col min="10" max="10" width="4.3046875" style="49" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" style="49" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" style="49" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" style="49" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="28.3046875" customWidth="1"/>
+    <col min="13" max="13" width="28.28515625" customWidth="1"/>
     <col min="14" max="14" width="6" style="43" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.3046875" style="43" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.3828125" style="44" customWidth="1"/>
-    <col min="18" max="18" width="4.3828125" style="44" customWidth="1"/>
-    <col min="19" max="19" width="6.61328125" style="44" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" style="43" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="44" customWidth="1"/>
+    <col min="18" max="18" width="6" style="44" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" style="44" customWidth="1"/>
     <col min="20" max="20" width="5" style="44" customWidth="1"/>
-    <col min="21" max="21" width="66.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.84375" style="44" customWidth="1"/>
-    <col min="23" max="23" width="7.53515625" style="44" customWidth="1"/>
+    <col min="21" max="21" width="66.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.85546875" style="44" customWidth="1"/>
+    <col min="23" max="23" width="7.5703125" style="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>91</v>
       </c>
@@ -6404,12 +6404,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>2</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>94</v>
@@ -6421,16 +6421,16 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="J2" s="60" t="s">
         <v>1</v>
@@ -6439,13 +6439,13 @@
         <v>1</v>
       </c>
       <c r="L2" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M2" s="50" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N2" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O2" s="50">
         <v>255</v>
@@ -6476,12 +6476,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>3</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C3" s="20" t="s">
         <v>95</v>
@@ -6493,16 +6493,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I3" s="35" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="J3" s="60" t="s">
         <v>1</v>
@@ -6511,13 +6511,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M3" s="50" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N3" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="O3" s="50">
         <v>255</v>
@@ -6548,12 +6548,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>4</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>96</v>
@@ -6565,16 +6565,16 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="J4" s="60" t="s">
         <v>1</v>
@@ -6583,13 +6583,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M4" s="50" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="O4" s="50">
         <v>255</v>
@@ -6620,12 +6620,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>5</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>97</v>
@@ -6637,16 +6637,16 @@
         <v>1</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="J5" s="60" t="s">
         <v>1</v>
@@ -6655,13 +6655,13 @@
         <v>1</v>
       </c>
       <c r="L5" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M5" s="50" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>111</v>
+        <v>357</v>
       </c>
       <c r="O5" s="50">
         <v>255</v>
@@ -6692,15 +6692,15 @@
         <v>null</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>6</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>1</v>
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H6" s="60" t="s">
         <v>1</v>
@@ -6727,25 +6727,25 @@
         <v>1</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M6" s="50" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O6" s="50">
         <v>255</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q6" s="50">
         <v>0</v>
       </c>
       <c r="R6" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S6" s="50">
         <v>0</v>
@@ -6757,22 +6757,22 @@
         <v>1</v>
       </c>
       <c r="V6" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W6" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W6:W10" si="1">IF(OR(V6="cor.rgb",V6="cor.cmy",V6="cor.rgba",V6="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O6,".",Q6,".",S6,".",U6,""""), ".null",""), V6)</f>
         <v>"255.0.0"</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>7</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>1</v>
@@ -6781,10 +6781,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H7" s="60" t="s">
         <v>1</v>
@@ -6799,25 +6799,25 @@
         <v>1</v>
       </c>
       <c r="L7" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M7" s="50" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="N7" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O7" s="50">
         <v>0</v>
       </c>
       <c r="P7" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q7" s="50">
         <v>255</v>
       </c>
       <c r="R7" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S7" s="50">
         <v>0</v>
@@ -6829,22 +6829,22 @@
         <v>1</v>
       </c>
       <c r="V7" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W7" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>"0.255.0"</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>8</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>1</v>
@@ -6853,10 +6853,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H8" s="60" t="s">
         <v>1</v>
@@ -6871,25 +6871,25 @@
         <v>1</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M8" s="50" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O8" s="50">
         <v>0</v>
       </c>
       <c r="P8" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q8" s="50">
         <v>0</v>
       </c>
       <c r="R8" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S8" s="50">
         <v>255</v>
@@ -6901,22 +6901,22 @@
         <v>1</v>
       </c>
       <c r="V8" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W8" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>"0.0.255"</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>9</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>1</v>
@@ -6925,10 +6925,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H9" s="60" t="s">
         <v>1</v>
@@ -6943,25 +6943,25 @@
         <v>1</v>
       </c>
       <c r="L9" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M9" s="50" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O9" s="50">
         <v>200</v>
       </c>
       <c r="P9" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q9" s="50">
         <v>200</v>
       </c>
       <c r="R9" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S9" s="50">
         <v>200</v>
@@ -6973,22 +6973,22 @@
         <v>1</v>
       </c>
       <c r="V9" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W9" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>"200.200.200"</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>10</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>1</v>
@@ -6997,10 +6997,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H10" s="60" t="s">
         <v>1</v>
@@ -7015,25 +7015,25 @@
         <v>1</v>
       </c>
       <c r="L10" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M10" s="50" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O10" s="50">
         <v>120</v>
       </c>
       <c r="P10" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q10" s="50">
         <v>120</v>
       </c>
       <c r="R10" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S10" s="50">
         <v>120</v>
@@ -7045,22 +7045,22 @@
         <v>1</v>
       </c>
       <c r="V10" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W10" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>"120.120.120"</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>11</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D11" s="32" t="s">
         <v>1</v>
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H11" s="60" t="s">
         <v>1</v>
@@ -7087,25 +7087,25 @@
         <v>1</v>
       </c>
       <c r="L11" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M11" s="50" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O11" s="50">
         <v>20</v>
       </c>
       <c r="P11" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q11" s="50">
         <v>20</v>
       </c>
       <c r="R11" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S11" s="50">
         <v>20</v>
@@ -7117,22 +7117,22 @@
         <v>1</v>
       </c>
       <c r="V11" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W11" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(V11="cor.rgb",V11="cor.cmy",V11="cor.rgba",V11="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O11,".",Q11,".",S11,".",U11,""""), ".null",""), V11)</f>
         <v>"20.20.20"</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>12</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>1</v>
@@ -7141,10 +7141,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H12" s="60" t="s">
         <v>1</v>
@@ -7159,25 +7159,25 @@
         <v>1</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M12" s="50" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O12" s="50">
         <v>150</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q12" s="50">
         <v>30</v>
       </c>
       <c r="R12" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S12" s="50">
         <v>10</v>
@@ -7189,22 +7189,22 @@
         <v>1</v>
       </c>
       <c r="V12" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W12" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(V12="cor.rgb",V12="cor.cmy",V12="cor.rgba",V12="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O12,".",Q12,".",S12,".",U12,""""), ".null",""), V12)</f>
         <v>"150.30.10"</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>13</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>1</v>
@@ -7213,10 +7213,10 @@
         <v>1</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H13" s="60" t="s">
         <v>1</v>
@@ -7231,25 +7231,25 @@
         <v>1</v>
       </c>
       <c r="L13" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M13" s="50" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="O13" s="50">
         <v>150</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="Q13" s="50">
         <v>40</v>
       </c>
       <c r="R13" s="46" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="S13" s="50">
         <v>10</v>
@@ -7261,22 +7261,22 @@
         <v>1</v>
       </c>
       <c r="V13" s="46" t="s">
-        <v>121</v>
+        <v>361</v>
       </c>
       <c r="W13" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W13:W15" si="2">IF(OR(V13="cor.rgb",V13="cor.cmy",V13="cor.rgba",V13="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O13,".",Q13,".",S13,".",U13,""""), ".null",""), V13)</f>
         <v>"150.40.10"</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>14</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>1</v>
@@ -7285,10 +7285,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H14" s="60" t="s">
         <v>1</v>
@@ -7303,25 +7303,25 @@
         <v>1</v>
       </c>
       <c r="L14" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M14" s="50" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>143</v>
+        <v>358</v>
       </c>
       <c r="O14" s="50">
         <v>150</v>
       </c>
       <c r="P14" s="47" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="Q14" s="50">
         <v>50</v>
       </c>
       <c r="R14" s="46" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="S14" s="50">
         <v>10</v>
@@ -7333,22 +7333,22 @@
         <v>1</v>
       </c>
       <c r="V14" s="46" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="W14" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>"150.50.10"</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>15</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>1</v>
@@ -7357,10 +7357,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H15" s="60" t="s">
         <v>1</v>
@@ -7375,25 +7375,25 @@
         <v>1</v>
       </c>
       <c r="L15" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M15" s="50" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>143</v>
+        <v>358</v>
       </c>
       <c r="O15" s="50">
         <v>150</v>
       </c>
       <c r="P15" s="47" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="Q15" s="50">
         <v>60</v>
       </c>
       <c r="R15" s="46" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="S15" s="50">
         <v>10</v>
@@ -7405,64 +7405,64 @@
         <v>1</v>
       </c>
       <c r="V15" s="46" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="W15" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>"150.60.10"</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33">
         <v>16</v>
       </c>
       <c r="B16" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="M16" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="O16" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="P16" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="M16" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="N16" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="O16" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="P16" s="46" t="s">
-        <v>147</v>
-      </c>
       <c r="Q16" s="50" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="R16" s="47" t="s">
         <v>1</v>
@@ -7484,57 +7484,57 @@
         <v>null</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>17</v>
       </c>
       <c r="B17" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="M17" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="N17" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="O17" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="P17" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="M17" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="N17" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="O17" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="P17" s="46" t="s">
-        <v>150</v>
-      </c>
       <c r="Q17" s="50" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="R17" s="47" t="s">
         <v>1</v>
@@ -7543,10 +7543,10 @@
         <v>1</v>
       </c>
       <c r="T17" s="46" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="U17" s="50" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="V17" s="46" t="s">
         <v>1</v>
@@ -7556,15 +7556,15 @@
         <v>null</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
         <v>18</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>1</v>
@@ -7591,10 +7591,10 @@
         <v>1</v>
       </c>
       <c r="L18" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M18" s="50" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="N18" s="55" t="s">
         <v>1</v>
@@ -7628,15 +7628,15 @@
         <v>null</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>19</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D19" s="32" t="s">
         <v>1</v>
@@ -7663,10 +7663,10 @@
         <v>1</v>
       </c>
       <c r="L19" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M19" s="50" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="N19" s="55" t="s">
         <v>1</v>
@@ -7700,15 +7700,15 @@
         <v>null</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>20</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D20" s="32" t="s">
         <v>1</v>
@@ -7735,10 +7735,10 @@
         <v>1</v>
       </c>
       <c r="L20" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M20" s="50" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="N20" s="55" t="s">
         <v>1</v>
@@ -7772,15 +7772,15 @@
         <v>null</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>21</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D21" s="32" t="s">
         <v>1</v>
@@ -7807,10 +7807,10 @@
         <v>1</v>
       </c>
       <c r="L21" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M21" s="50" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="N21" s="55" t="s">
         <v>1</v>
@@ -7844,27 +7844,27 @@
         <v>null</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>22</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F22" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H22" s="60" t="s">
         <v>1</v>
@@ -7879,25 +7879,25 @@
         <v>1</v>
       </c>
       <c r="L22" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M22" s="50" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="N22" s="47" t="s">
-        <v>143</v>
+        <v>358</v>
       </c>
       <c r="O22" s="50">
         <v>0</v>
       </c>
       <c r="P22" s="47" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="Q22" s="50">
         <v>0</v>
       </c>
       <c r="R22" s="46" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="S22" s="50">
         <v>100</v>
@@ -7909,34 +7909,34 @@
         <v>1</v>
       </c>
       <c r="V22" s="46" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="W22" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W22:W24" si="3">IF(OR(V22="cor.rgb",V22="cor.cmy",V22="cor.rgba",V22="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O22,".",Q22,".",S22,".",U22,""""), ".null",""), V22)</f>
         <v>"0.0.100"</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>23</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H23" s="60" t="s">
         <v>1</v>
@@ -7951,25 +7951,25 @@
         <v>1</v>
       </c>
       <c r="L23" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M23" s="50" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="N23" s="47" t="s">
-        <v>143</v>
+        <v>358</v>
       </c>
       <c r="O23" s="50">
         <v>63</v>
       </c>
       <c r="P23" s="47" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="Q23" s="50">
         <v>23</v>
       </c>
       <c r="R23" s="46" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="S23" s="50">
         <v>100</v>
@@ -7981,34 +7981,34 @@
         <v>1</v>
       </c>
       <c r="V23" s="46" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="W23" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>"63.23.100"</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>24</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H24" s="60" t="s">
         <v>1</v>
@@ -8023,25 +8023,25 @@
         <v>1</v>
       </c>
       <c r="L24" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M24" s="50" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="N24" s="47" t="s">
-        <v>143</v>
+        <v>358</v>
       </c>
       <c r="O24" s="50">
         <v>100</v>
       </c>
       <c r="P24" s="47" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="Q24" s="50">
         <v>0</v>
       </c>
       <c r="R24" s="46" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="S24" s="50">
         <v>100</v>
@@ -8053,22 +8053,22 @@
         <v>1</v>
       </c>
       <c r="V24" s="46" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="W24" s="50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>"100.0.100"</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>25</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D25" s="32" t="s">
         <v>1</v>
@@ -8095,10 +8095,10 @@
         <v>1</v>
       </c>
       <c r="L25" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M25" s="50" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="N25" s="55" t="s">
         <v>1</v>
@@ -8131,21 +8131,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>26</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E26" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F26" s="32" t="s">
         <v>1</v>
@@ -8166,10 +8166,10 @@
         <v>1</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M26" s="50" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="N26" s="55" t="s">
         <v>1</v>
@@ -8202,22 +8202,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>27</v>
       </c>
       <c r="B27" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="C27" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>172</v>
-      </c>
       <c r="F27" s="32" t="s">
         <v>1</v>
       </c>
@@ -8237,10 +8237,10 @@
         <v>1</v>
       </c>
       <c r="L27" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M27" s="50" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="N27" s="55" t="s">
         <v>1</v>
@@ -8273,21 +8273,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>28</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E28" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F28" s="32" t="s">
         <v>1</v>
@@ -8308,10 +8308,10 @@
         <v>1</v>
       </c>
       <c r="L28" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M28" s="50" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="N28" s="55" t="s">
         <v>1</v>
@@ -8344,21 +8344,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>29</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E29" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F29" s="32" t="s">
         <v>1</v>
@@ -8379,10 +8379,10 @@
         <v>1</v>
       </c>
       <c r="L29" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M29" s="50" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="N29" s="55" t="s">
         <v>1</v>
@@ -8415,21 +8415,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>30</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E30" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F30" s="32" t="s">
         <v>1</v>
@@ -8450,10 +8450,10 @@
         <v>1</v>
       </c>
       <c r="L30" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M30" s="50" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="N30" s="55" t="s">
         <v>1</v>
@@ -8486,21 +8486,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>31</v>
       </c>
       <c r="B31" s="53" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E31" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F31" s="32" t="s">
         <v>1</v>
@@ -8521,10 +8521,10 @@
         <v>1</v>
       </c>
       <c r="L31" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M31" s="50" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="N31" s="55" t="s">
         <v>1</v>
@@ -8557,21 +8557,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>32</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E32" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F32" s="32" t="s">
         <v>1</v>
@@ -8592,10 +8592,10 @@
         <v>1</v>
       </c>
       <c r="L32" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M32" s="50" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="N32" s="55" t="s">
         <v>1</v>
@@ -8628,21 +8628,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>33</v>
       </c>
       <c r="B33" s="53" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E33" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F33" s="32" t="s">
         <v>1</v>
@@ -8663,10 +8663,10 @@
         <v>1</v>
       </c>
       <c r="L33" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M33" s="50" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="N33" s="55" t="s">
         <v>1</v>
@@ -8699,21 +8699,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>34</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E34" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F34" s="32" t="s">
         <v>1</v>
@@ -8734,10 +8734,10 @@
         <v>1</v>
       </c>
       <c r="L34" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M34" s="50" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="N34" s="55" t="s">
         <v>1</v>
@@ -8770,21 +8770,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>35</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E35" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F35" s="32" t="s">
         <v>1</v>
@@ -8805,10 +8805,10 @@
         <v>1</v>
       </c>
       <c r="L35" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M35" s="50" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="N35" s="55" t="s">
         <v>1</v>
@@ -8841,21 +8841,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>36</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E36" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F36" s="32" t="s">
         <v>1</v>
@@ -8876,10 +8876,10 @@
         <v>1</v>
       </c>
       <c r="L36" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M36" s="50" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="N36" s="55" t="s">
         <v>1</v>
@@ -8912,21 +8912,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>37</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E37" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F37" s="32" t="s">
         <v>1</v>
@@ -8947,10 +8947,10 @@
         <v>1</v>
       </c>
       <c r="L37" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M37" s="50" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="N37" s="55" t="s">
         <v>1</v>
@@ -8983,21 +8983,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>38</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E38" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F38" s="32" t="s">
         <v>1</v>
@@ -9018,10 +9018,10 @@
         <v>1</v>
       </c>
       <c r="L38" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M38" s="50" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="N38" s="55" t="s">
         <v>1</v>
@@ -9054,21 +9054,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>39</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E39" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F39" s="32" t="s">
         <v>1</v>
@@ -9089,10 +9089,10 @@
         <v>1</v>
       </c>
       <c r="L39" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M39" s="50" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="N39" s="55" t="s">
         <v>1</v>
@@ -9125,21 +9125,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>40</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E40" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F40" s="32" t="s">
         <v>1</v>
@@ -9160,10 +9160,10 @@
         <v>1</v>
       </c>
       <c r="L40" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M40" s="50" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="N40" s="55" t="s">
         <v>1</v>
@@ -9196,21 +9196,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>41</v>
       </c>
       <c r="B41" s="53" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E41" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F41" s="32" t="s">
         <v>1</v>
@@ -9231,10 +9231,10 @@
         <v>1</v>
       </c>
       <c r="L41" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M41" s="50" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="N41" s="55" t="s">
         <v>1</v>
@@ -9267,21 +9267,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>42</v>
       </c>
       <c r="B42" s="53" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E42" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F42" s="32" t="s">
         <v>1</v>
@@ -9302,10 +9302,10 @@
         <v>1</v>
       </c>
       <c r="L42" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M42" s="50" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="N42" s="55" t="s">
         <v>1</v>
@@ -9338,21 +9338,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>43</v>
       </c>
       <c r="B43" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C43" s="20" t="s">
-        <v>187</v>
-      </c>
       <c r="D43" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E43" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F43" s="32" t="s">
         <v>1</v>
@@ -9373,10 +9373,10 @@
         <v>1</v>
       </c>
       <c r="L43" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M43" s="50" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N43" s="55" t="s">
         <v>1</v>
@@ -9409,21 +9409,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>44</v>
       </c>
       <c r="B44" s="53" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E44" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F44" s="32" t="s">
         <v>1</v>
@@ -9444,10 +9444,10 @@
         <v>1</v>
       </c>
       <c r="L44" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M44" s="50" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="N44" s="55" t="s">
         <v>1</v>
@@ -9480,21 +9480,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>45</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E45" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F45" s="32" t="s">
         <v>1</v>
@@ -9515,10 +9515,10 @@
         <v>1</v>
       </c>
       <c r="L45" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M45" s="50" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N45" s="55" t="s">
         <v>1</v>
@@ -9551,21 +9551,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>46</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E46" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F46" s="32" t="s">
         <v>1</v>
@@ -9586,10 +9586,10 @@
         <v>1</v>
       </c>
       <c r="L46" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M46" s="50" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="N46" s="55" t="s">
         <v>1</v>
@@ -9622,21 +9622,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>47</v>
       </c>
       <c r="B47" s="53" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E47" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F47" s="32" t="s">
         <v>1</v>
@@ -9657,10 +9657,10 @@
         <v>1</v>
       </c>
       <c r="L47" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M47" s="50" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N47" s="55" t="s">
         <v>1</v>
@@ -9693,21 +9693,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>48</v>
       </c>
       <c r="B48" s="53" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E48" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F48" s="32" t="s">
         <v>1</v>
@@ -9728,10 +9728,10 @@
         <v>1</v>
       </c>
       <c r="L48" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M48" s="50" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="N48" s="55" t="s">
         <v>1</v>
@@ -9764,21 +9764,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>49</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E49" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F49" s="32" t="s">
         <v>1</v>
@@ -9799,10 +9799,10 @@
         <v>1</v>
       </c>
       <c r="L49" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M49" s="50" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="N49" s="55" t="s">
         <v>1</v>
@@ -9835,21 +9835,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>50</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E50" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F50" s="32" t="s">
         <v>1</v>
@@ -9870,10 +9870,10 @@
         <v>1</v>
       </c>
       <c r="L50" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M50" s="50" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="N50" s="55" t="s">
         <v>1</v>
@@ -9906,21 +9906,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="33">
         <v>51</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E51" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F51" s="32" t="s">
         <v>1</v>
@@ -9941,10 +9941,10 @@
         <v>1</v>
       </c>
       <c r="L51" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M51" s="50" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N51" s="55" t="s">
         <v>1</v>
@@ -9977,21 +9977,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="33">
         <v>52</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E52" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F52" s="32" t="s">
         <v>1</v>
@@ -10012,16 +10012,16 @@
         <v>1</v>
       </c>
       <c r="L52" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M52" s="58" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="N52" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O52" s="56" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="P52" s="47" t="s">
         <v>1</v>
@@ -10030,16 +10030,16 @@
         <v>1</v>
       </c>
       <c r="R52" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S52" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T52" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U52" s="56" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="V52" s="47" t="s">
         <v>1</v>
@@ -10048,21 +10048,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <v>53</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E53" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F53" s="32" t="s">
         <v>1</v>
@@ -10083,16 +10083,16 @@
         <v>1</v>
       </c>
       <c r="L53" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M53" s="58" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="N53" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O53" s="50" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="P53" s="47" t="s">
         <v>1</v>
@@ -10101,16 +10101,16 @@
         <v>1</v>
       </c>
       <c r="R53" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S53" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T53" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U53" s="56" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="V53" s="47" t="s">
         <v>1</v>
@@ -10119,21 +10119,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>54</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E54" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F54" s="32" t="s">
         <v>1</v>
@@ -10154,16 +10154,16 @@
         <v>1</v>
       </c>
       <c r="L54" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M54" s="58" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="N54" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O54" s="56" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="P54" s="47" t="s">
         <v>1</v>
@@ -10172,16 +10172,16 @@
         <v>1</v>
       </c>
       <c r="R54" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S54" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T54" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U54" s="56" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="V54" s="47" t="s">
         <v>1</v>
@@ -10190,21 +10190,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
         <v>55</v>
       </c>
       <c r="B55" s="53" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E55" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F55" s="32" t="s">
         <v>1</v>
@@ -10225,16 +10225,16 @@
         <v>1</v>
       </c>
       <c r="L55" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M55" s="58" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="N55" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O55" s="56" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="P55" s="47" t="s">
         <v>1</v>
@@ -10243,16 +10243,16 @@
         <v>1</v>
       </c>
       <c r="R55" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S55" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T55" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U55" s="56" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="V55" s="47" t="s">
         <v>1</v>
@@ -10261,21 +10261,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>56</v>
       </c>
       <c r="B56" s="53" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E56" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F56" s="32" t="s">
         <v>1</v>
@@ -10296,16 +10296,16 @@
         <v>1</v>
       </c>
       <c r="L56" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M56" s="58" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N56" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O56" s="56" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="P56" s="47" t="s">
         <v>1</v>
@@ -10314,16 +10314,16 @@
         <v>1</v>
       </c>
       <c r="R56" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S56" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T56" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U56" s="56" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="V56" s="47" t="s">
         <v>1</v>
@@ -10332,21 +10332,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
         <v>57</v>
       </c>
       <c r="B57" s="53" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E57" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F57" s="32" t="s">
         <v>1</v>
@@ -10367,16 +10367,16 @@
         <v>1</v>
       </c>
       <c r="L57" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M57" s="58" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="N57" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O57" s="56" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="P57" s="47" t="s">
         <v>1</v>
@@ -10385,16 +10385,16 @@
         <v>1</v>
       </c>
       <c r="R57" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S57" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T57" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U57" s="56" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="V57" s="47" t="s">
         <v>1</v>
@@ -10403,69 +10403,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>58</v>
       </c>
       <c r="B58" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="54" t="s">
+        <v>163</v>
+      </c>
+      <c r="F58" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="K58" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="L58" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="M58" s="58" t="s">
+        <v>211</v>
+      </c>
+      <c r="N58" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="O58" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="P58" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="R58" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="S58" s="50" t="s">
+        <v>228</v>
+      </c>
+      <c r="T58" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="C58" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" s="54" t="s">
-        <v>172</v>
-      </c>
-      <c r="F58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="K58" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="L58" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="M58" s="58" t="s">
-        <v>220</v>
-      </c>
-      <c r="N58" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="O58" s="56" t="s">
-        <v>202</v>
-      </c>
-      <c r="P58" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q58" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="R58" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="S58" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="T58" s="46" t="s">
-        <v>225</v>
-      </c>
       <c r="U58" s="56" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="V58" s="47" t="s">
         <v>1</v>
@@ -10474,21 +10474,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>59</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E59" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F59" s="32" t="s">
         <v>1</v>
@@ -10509,16 +10509,16 @@
         <v>1</v>
       </c>
       <c r="L59" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M59" s="58" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="N59" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O59" s="56" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="P59" s="47" t="s">
         <v>1</v>
@@ -10527,16 +10527,16 @@
         <v>1</v>
       </c>
       <c r="R59" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S59" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T59" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U59" s="56" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="V59" s="47" t="s">
         <v>1</v>
@@ -10545,21 +10545,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="33">
         <v>60</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E60" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F60" s="32" t="s">
         <v>1</v>
@@ -10580,16 +10580,16 @@
         <v>1</v>
       </c>
       <c r="L60" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M60" s="58" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N60" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O60" s="56" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="P60" s="47" t="s">
         <v>1</v>
@@ -10598,17 +10598,17 @@
         <v>1</v>
       </c>
       <c r="R60" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S60" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T60" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="U60" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="U60" s="56" t="s">
-        <v>234</v>
-      </c>
       <c r="V60" s="47" t="s">
         <v>1</v>
       </c>
@@ -10616,21 +10616,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>61</v>
       </c>
       <c r="B61" s="53" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E61" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F61" s="32" t="s">
         <v>1</v>
@@ -10651,17 +10651,17 @@
         <v>1</v>
       </c>
       <c r="L61" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M61" s="58" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N61" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="O61" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="O61" s="56" t="s">
-        <v>203</v>
-      </c>
       <c r="P61" s="47" t="s">
         <v>1</v>
       </c>
@@ -10669,16 +10669,16 @@
         <v>1</v>
       </c>
       <c r="R61" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S61" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T61" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U61" s="56" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="V61" s="47" t="s">
         <v>1</v>
@@ -10687,21 +10687,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="33">
         <v>62</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E62" s="54" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F62" s="32" t="s">
         <v>1</v>
@@ -10722,16 +10722,16 @@
         <v>1</v>
       </c>
       <c r="L62" s="46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M62" s="58" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="N62" s="57" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O62" s="56" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="P62" s="47" t="s">
         <v>1</v>
@@ -10740,16 +10740,16 @@
         <v>1</v>
       </c>
       <c r="R62" s="47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S62" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="T62" s="46" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U62" s="56" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="V62" s="47" t="s">
         <v>1</v>
@@ -10763,7 +10763,7 @@
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD17 A18:B18 A19:XFD19 A20:B21 A22:XFD1048576">
+  <conditionalFormatting sqref="A18:B18 A19:XFD19 A20:B21 A1:XFD17 A22:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -10794,15 +10794,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.3046875" customWidth="1"/>
-    <col min="4" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -10876,10 +10876,10 @@
         <v>28</v>
       </c>
       <c r="C7" s="79" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -10887,10 +10887,10 @@
         <v>37</v>
       </c>
       <c r="C8" s="79" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -10898,10 +10898,10 @@
         <v>36</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -10909,10 +10909,10 @@
         <v>35</v>
       </c>
       <c r="C10" s="79" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -10920,10 +10920,10 @@
         <v>34</v>
       </c>
       <c r="C11" s="79" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -10931,10 +10931,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="79" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -10942,10 +10942,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="79" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -10953,10 +10953,10 @@
         <v>31</v>
       </c>
       <c r="C14" s="79" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -10964,50 +10964,50 @@
         <v>30</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C16" s="31" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C17" s="31" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C18" s="31" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C19" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C20" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C21" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C22" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C23" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C24" s="78" t="s">
         <v>1</v>
       </c>

--- a/Versão5/CROM/Ontologia_CROMA.xlsx
+++ b/Versão5/CROM/Ontologia_CROMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CROM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D024D10F-9464-4276-A4FF-B2F10CE00F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7387EF1F-07BD-4407-83EA-6927E33C2DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46191.452614699076</v>
+        <v>46191.463891203704</v>
       </c>
       <c r="C18" s="64" t="s">
         <v>256</v>
@@ -6544,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="50" t="str">
-        <f t="shared" ref="W3:W24" si="0">IF(OR(V3="rgb",V3="cmy",V3="rgba",V3="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O3,".",Q3,".",S3,".",U3,""""), ".null",""), V3)</f>
+        <f t="shared" ref="W3:W17" si="0">IF(OR(V3="rgb",V3="cmy",V3="rgba",V3="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O3,".",Q3,".",S3,".",U3,""""), ".null",""), V3)</f>
         <v>null</v>
       </c>
     </row>
@@ -6637,10 +6637,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>337</v>
+        <v>1</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>125</v>
@@ -10763,7 +10763,7 @@
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A18:B18 A19:XFD19 A20:B21 A1:XFD17 A22:XFD1048576">
+  <conditionalFormatting sqref="A18:B18 A19:XFD19 A20:B21 A22:XFD1048576 A1:XFD17">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>

--- a/Versão5/CROM/Ontologia_CROMA.xlsx
+++ b/Versão5/CROM/Ontologia_CROMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CROM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7387EF1F-07BD-4407-83EA-6927E33C2DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F862740-B997-4E10-89D4-9A62EA6B2CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -3451,15 +3451,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3648,19 +3648,19 @@
         <v>256</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46191.463891203704</v>
+        <v>46214.368290393519</v>
       </c>
       <c r="C18" s="64" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="43" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>261</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="43" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>259</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="43" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>260</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>253</v>
       </c>
@@ -3759,33 +3759,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AA24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" customWidth="1"/>
+    <col min="2" max="2" width="5.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3046875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" customWidth="1"/>
-    <col min="7" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47.28515625" customWidth="1"/>
-    <col min="12" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.15234375" customWidth="1"/>
+    <col min="7" max="9" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3828125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.3046875" customWidth="1"/>
+    <col min="12" max="14" width="7.53515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="101.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="98.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="101.53515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="98.3828125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.84375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.140625" customWidth="1"/>
-    <col min="25" max="25" width="5.140625" customWidth="1"/>
-    <col min="26" max="26" width="5.7109375" customWidth="1"/>
-    <col min="27" max="27" width="79.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.15234375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.84375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.15234375" customWidth="1"/>
+    <col min="25" max="25" width="5.15234375" customWidth="1"/>
+    <col min="26" max="26" width="5.69140625" customWidth="1"/>
+    <col min="27" max="27" width="79.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="67">
         <v>2</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="67">
         <v>3</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="67">
         <v>4</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="67">
         <v>5</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="67">
         <v>6</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="67">
         <v>7</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>Amount of cyan color that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="67">
         <v>8</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>Amount of magenta color that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="67">
         <v>9</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>Amount of yellow color between which can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="67">
         <v>10</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>Amount of black color between which can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="67">
         <v>11</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>Amount of red color that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="67">
         <v>12</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>Amount of green color between that can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="67">
         <v>13</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>Amount of blue color between that can vary from 0 to 255.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="67">
         <v>14</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>Amount of transparency that can vary between 0 and 255.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="67">
         <v>15</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>Digital color composed of CMY channels.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="67">
         <v>16</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>Digital color composed of CMYB channels.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="67">
         <v>17</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>Digital color composed of RGB channels.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="67">
         <v>18</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>Digital color composed of RGBA channels. Channel A defines transparency.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="67">
         <v>19</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>Munsell Color System: Hue Parameter.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="67">
         <v>20</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>Munsell color system: Luminosity parameter.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="67">
         <v>21</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>Munsell Color System: Parameter Chroma. It is the degree of distance of a color from the neutral color of the same value. A low chroma weakens the color. A high chroma for saturated, strong, or vivid color.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="67">
         <v>22</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>Munsell system-specific color.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="67">
         <v>23</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>Specific color from the Pantone catalog.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="67">
         <v>24</v>
       </c>
@@ -6046,15 +6046,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
         <v>22</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="41">
         <v>2</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="41">
         <v>3</v>
       </c>
@@ -6264,14 +6264,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="38">
         <v>1</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -6306,34 +6306,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" style="49" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" style="49" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="49" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="28.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6" style="43" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" style="43" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="44" customWidth="1"/>
-    <col min="18" max="18" width="6" style="44" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" style="44" customWidth="1"/>
-    <col min="20" max="20" width="5" style="44" customWidth="1"/>
-    <col min="21" max="21" width="66.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.85546875" style="44" customWidth="1"/>
-    <col min="23" max="23" width="7.5703125" style="44" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.84375" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.23046875" style="49" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.4609375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.765625" style="43" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.84375" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.765625" style="43" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.4609375" style="44" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.921875" style="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="52" t="s">
         <v>91</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>"255.0.0"</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="33">
         <v>7</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>"0.255.0"</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>"0.0.255"</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>"200.200.200"</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>"120.120.120"</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>"20.20.20"</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="33">
         <v>12</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>"150.30.10"</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="33">
         <v>13</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>"150.40.10"</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="33">
         <v>14</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>"150.50.10"</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="33">
         <v>15</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>"150.60.10"</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="33">
         <v>16</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="33">
         <v>17</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="33">
         <v>18</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="33">
         <v>19</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="33">
         <v>20</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="33">
         <v>21</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="33">
         <v>22</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>"0.0.100"</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="33">
         <v>23</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>"63.23.100"</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="33">
         <v>24</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>"100.0.100"</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="33">
         <v>25</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="33">
         <v>26</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33">
         <v>27</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33">
         <v>28</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="33">
         <v>29</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="33">
         <v>30</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="33">
         <v>31</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="33">
         <v>32</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="33">
         <v>33</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="33">
         <v>34</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="33">
         <v>35</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="33">
         <v>36</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="33">
         <v>37</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="33">
         <v>38</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="33">
         <v>39</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="33">
         <v>40</v>
       </c>
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="33">
         <v>41</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="33">
         <v>42</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="33">
         <v>43</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="33">
         <v>44</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="33">
         <v>45</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="33">
         <v>46</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="33">
         <v>47</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="33">
         <v>48</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="33">
         <v>49</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="33">
         <v>50</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="33">
         <v>51</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="33">
         <v>52</v>
       </c>
@@ -10048,7 +10048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="33">
         <v>53</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="33">
         <v>54</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="33">
         <v>55</v>
       </c>
@@ -10261,7 +10261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="33">
         <v>56</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="33">
         <v>57</v>
       </c>
@@ -10403,7 +10403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="33">
         <v>58</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="33">
         <v>59</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="33">
         <v>60</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="33">
         <v>61</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="33">
         <v>62</v>
       </c>
@@ -10763,7 +10763,7 @@
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A18:B18 A19:XFD19 A20:B21 A22:XFD1048576 A1:XFD17">
+  <conditionalFormatting sqref="A1:XFD17 A18:B18 A19:XFD19 A20:B21 A22:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -10794,15 +10794,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.3046875" customWidth="1"/>
+    <col min="4" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -10901,7 +10901,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -10967,47 +10967,47 @@
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C16" s="31" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C17" s="31" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C18" s="31" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C19" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C20" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C21" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C22" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C23" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C24" s="78" t="s">
         <v>1</v>
       </c>

--- a/Versão5/CROM/Ontologia_CROMA.xlsx
+++ b/Versão5/CROM/Ontologia_CROMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CROM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC587A19-8ADA-4A48-8F28-ACBA9CFDCD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654A4936-4477-4761-BF44-47B722367C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="348">
   <si>
     <t>Key</t>
   </si>
@@ -2056,45 +2056,6 @@
     <t>"Canal de transparência Alfa"</t>
   </si>
   <si>
-    <t>Contêiner</t>
-  </si>
-  <si>
-    <t>Informação</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Requisito.Espacial</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Mobiliário</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Equipamento</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Sistemas</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>"Cor Pantone utilizada no catálogo do DNIT"</t>
   </si>
   <si>
@@ -2335,12 +2296,6 @@
     <t>cor.cmy</t>
   </si>
   <si>
-    <t>Contêineres</t>
-  </si>
-  <si>
-    <t>[ 5I ]</t>
-  </si>
-  <si>
     <t>Conceitos</t>
   </si>
   <si>
@@ -2348,6 +2303,9 @@
   </si>
   <si>
     <t>Paletas</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
   </si>
 </sst>
 </file>
@@ -2717,7 +2675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2928,9 +2886,6 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2953,7 +2908,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="13">
     <dxf>
       <font>
         <b val="0"/>
@@ -3039,54 +2994,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3431,15 +3338,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="62" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3450,7 +3357,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3461,7 +3368,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3472,7 +3379,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3483,7 +3390,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3495,7 +3402,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3507,7 +3414,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3518,7 +3425,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3529,7 +3436,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3540,7 +3447,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3551,7 +3458,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3562,7 +3469,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3573,7 +3480,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3584,7 +3491,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3595,7 +3502,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3606,7 +3513,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3617,7 +3524,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3628,19 +3535,19 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46243.565698148152</v>
+        <v>46244.600059259261</v>
       </c>
       <c r="C18" s="61" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>258</v>
       </c>
@@ -3651,7 +3558,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>256</v>
       </c>
@@ -3663,7 +3570,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>257</v>
       </c>
@@ -3675,7 +3582,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3686,7 +3593,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3697,7 +3604,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3708,7 +3615,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3719,7 +3626,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>250</v>
       </c>
@@ -3738,36 +3645,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AA24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AA19"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.53515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="108.15234375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="110.84375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.15234375" style="70" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.3828125" style="70" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.69140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.69140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.53515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="108.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="110.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.42578125" style="70" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.7109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="70" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.85546875" style="70" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7" style="70" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.84375" style="70" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.15234375" style="70" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="70" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.140625" style="70" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="109" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
@@ -3786,19 +3693,19 @@
       <c r="F1" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="73" t="s">
+      <c r="G1" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="73" t="s">
+      <c r="H1" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="73" t="s">
+      <c r="I1" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="73" t="s">
+      <c r="J1" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="73" t="s">
+      <c r="K1" s="72" t="s">
         <v>43</v>
       </c>
       <c r="L1" s="24" t="s">
@@ -3834,7 +3741,7 @@
       <c r="V1" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="77" t="s">
+      <c r="W1" s="76" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="24" t="s">
@@ -3850,2168 +3757,1697 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="70" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64">
         <v>2</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="E2" s="72" t="s">
-        <v>357</v>
-      </c>
-      <c r="F2" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="65" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
-      </c>
-      <c r="M2" s="65" t="str">
+        <v>331</v>
+      </c>
+      <c r="L2" s="66" t="str">
+        <f>_xlfn.CONCAT(C2)</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M2" s="66" t="str">
+        <f t="shared" ref="M2:O17" si="0">_xlfn.CONCAT("", D2)</f>
+        <v>Paletas</v>
+      </c>
+      <c r="N2" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N2" s="65" t="str">
-        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Contêineres</v>
-      </c>
-      <c r="O2" s="65" t="str">
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="O2" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Cyan</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q2" s="66" t="str">
+        <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
+        <v>Cantidad de color cian que puede variar entre 0 y 255.</v>
+      </c>
+      <c r="R2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="60" t="str">
+        <f t="shared" ref="S2:U17" si="1">SUBSTITUTE(C2, "_", " ")</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="T2" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q2" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="R2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="60" t="str">
-        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Gestão</v>
-      </c>
-      <c r="T2" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U2" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <v>Paletas</v>
+      </c>
+      <c r="U2" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
       </c>
       <c r="V2" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="78" t="str">
-        <f>CONCATENATE("Key-CROMA-",A2)</f>
+      <c r="W2" s="77" t="str">
+        <f t="shared" ref="W2:W19" si="2">CONCATENATE("Key-CROMA-",A2)</f>
         <v>Key-CROMA-2</v>
       </c>
       <c r="X2" s="60" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="Y2" s="60" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="Z2" s="60" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="AA2" s="60" t="str">
-        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" s="70" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Amount of cyan color that can vary between 0 and 255.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>3</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="E3" s="72" t="s">
-        <v>357</v>
-      </c>
-      <c r="F3" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="65" t="str">
+        <v>332</v>
+      </c>
+      <c r="L3" s="66" t="str">
+        <f>_xlfn.CONCAT(C3)</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M3" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M3" s="65" t="str">
+        <v>Paletas</v>
+      </c>
+      <c r="N3" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N3" s="65" t="str">
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="O3" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Magenta</v>
+      </c>
+      <c r="P3" s="66" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q3" s="66" t="str">
+        <f t="shared" ref="Q3:Q19" si="3">_xlfn.TRANSLATE(P3,"pt","es")</f>
+        <v>Cantidad de color magenta que puede variar entre 0 y 255.</v>
+      </c>
+      <c r="R3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O3" s="65" t="str">
+        <v>Cromáticos</v>
+      </c>
+      <c r="T3" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Requisito Espacial</v>
-      </c>
-      <c r="P3" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q3" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="R3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T3" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U3" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <v>Paletas</v>
+      </c>
+      <c r="U3" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
       </c>
       <c r="V3" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="78" t="str">
-        <f t="shared" ref="W3:W24" si="4">CONCATENATE("Key-CROMA-",A3)</f>
+      <c r="W3" s="77" t="str">
+        <f t="shared" si="2"/>
         <v>Key-CROMA-3</v>
       </c>
       <c r="X3" s="60" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="Y3" s="60" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="Z3" s="60" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="AA3" s="60" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="70" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="AA3:AA19" si="4">_xlfn.TRANSLATE(P3,"pt","en")</f>
+        <v>Amount of magenta color that can vary between 0 and 255.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="64">
         <v>4</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>357</v>
-      </c>
-      <c r="F4" s="72" t="s">
-        <v>271</v>
-      </c>
-      <c r="G4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="65" t="str">
+        <v>333</v>
+      </c>
+      <c r="L4" s="66" t="str">
+        <f>_xlfn.CONCAT(C4)</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M4" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M4" s="65" t="str">
+        <v>Paletas</v>
+      </c>
+      <c r="N4" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N4" s="65" t="str">
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="O4" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Yellow</v>
+      </c>
+      <c r="P4" s="66" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q4" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v>La cantidad de color amarillo entre los cuales puede variar de 0 a 255.</v>
+      </c>
+      <c r="R4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O4" s="65" t="str">
+        <v>Cromáticos</v>
+      </c>
+      <c r="T4" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Requisito Mobiliário</v>
-      </c>
-      <c r="P4" s="60" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q4" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="R4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T4" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U4" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <v>Paletas</v>
+      </c>
+      <c r="U4" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
       </c>
       <c r="V4" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="78" t="str">
+      <c r="W4" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-4</v>
+      </c>
+      <c r="X4" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y4" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z4" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA4" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-4</v>
-      </c>
-      <c r="X4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="60" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="70" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Amount of yellow color between which can vary from 0 to 255.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>5</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C5" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="72" t="s">
-        <v>357</v>
-      </c>
-      <c r="F5" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="65" t="str">
+        <v>329</v>
+      </c>
+      <c r="L5" s="66" t="str">
+        <f t="shared" ref="L5:L19" si="5">_xlfn.CONCAT(C5)</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M5" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M5" s="65" t="str">
+        <v>Paletas</v>
+      </c>
+      <c r="N5" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N5" s="65" t="str">
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="O5" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Black</v>
+      </c>
+      <c r="P5" s="66" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q5" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v>La cantidad de color negro entre ellos puede variar de 0 a 255.</v>
+      </c>
+      <c r="R5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O5" s="65" t="str">
+        <v>Cromáticos</v>
+      </c>
+      <c r="T5" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Requisito Equipamento</v>
-      </c>
-      <c r="P5" s="60" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q5" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="R5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T5" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U5" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <v>Paletas</v>
+      </c>
+      <c r="U5" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
       </c>
       <c r="V5" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W5" s="78" t="str">
+      <c r="W5" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-5</v>
+      </c>
+      <c r="X5" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y5" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z5" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA5" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-5</v>
-      </c>
-      <c r="X5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="60" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" s="70" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Amount of black color between which can vary from 0 to 255.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="64">
         <v>6</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C6" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="72" t="s">
-        <v>357</v>
-      </c>
-      <c r="F6" s="72" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="65" t="str">
+        <v>330</v>
+      </c>
+      <c r="L6" s="66" t="str">
+        <f>_xlfn.CONCAT(C6)</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M6" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M6" s="65" t="str">
+        <v>Paletas</v>
+      </c>
+      <c r="N6" s="66" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N6" s="65" t="str">
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="O6" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Red</v>
+      </c>
+      <c r="P6" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q6" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v>Cantidad de color rojo que puede variar entre 0 y 255.</v>
+      </c>
+      <c r="R6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O6" s="65" t="str">
+        <v>Cromáticos</v>
+      </c>
+      <c r="T6" s="60" t="str">
         <f t="shared" si="1"/>
-        <v>Requisito Sistemas</v>
-      </c>
-      <c r="P6" s="60" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q6" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="R6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T6" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U6" s="60" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <v>Paletas</v>
+      </c>
+      <c r="U6" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
       </c>
       <c r="V6" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W6" s="78" t="str">
+      <c r="W6" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-6</v>
+      </c>
+      <c r="X6" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y6" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z6" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA6" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-6</v>
-      </c>
-      <c r="X6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="60" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Amount of red color that can vary between 0 and 255.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64">
         <v>7</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="G7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="75" t="s">
-        <v>344</v>
+        <v>94</v>
+      </c>
+      <c r="G7" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="74" t="s">
+        <v>328</v>
       </c>
       <c r="L7" s="66" t="str">
         <f>_xlfn.CONCAT(C7)</f>
         <v>Cromáticos</v>
       </c>
       <c r="M7" s="66" t="str">
-        <f t="shared" ref="M7:O22" si="5">_xlfn.CONCAT("", D7)</f>
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
       <c r="N7" s="66" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Canal.de.Cor</v>
       </c>
       <c r="O7" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Cyan</v>
+        <f t="shared" si="0"/>
+        <v>Green</v>
       </c>
       <c r="P7" s="66" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q7" s="66" t="str">
-        <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
-        <v>Cantidad de color cian que puede variar entre 0 y 255.</v>
+        <f t="shared" si="3"/>
+        <v>La cantidad de color verde entre eso puede variar de 0 a 255.</v>
       </c>
       <c r="R7" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="60" t="str">
-        <f t="shared" ref="S7:U22" si="6">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T7" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U7" s="65" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
       <c r="V7" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W7" s="78" t="str">
+      <c r="W7" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-7</v>
+      </c>
+      <c r="X7" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y7" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z7" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA7" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-7</v>
-      </c>
-      <c r="X7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="60" t="str">
-        <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Amount of cyan color that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Amount of green color between that can vary from 0 to 255.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="64">
         <v>8</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="G8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="75" t="s">
-        <v>345</v>
+        <v>95</v>
+      </c>
+      <c r="G8" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="74" t="s">
+        <v>334</v>
       </c>
       <c r="L8" s="66" t="str">
         <f>_xlfn.CONCAT(C8)</f>
         <v>Cromáticos</v>
       </c>
       <c r="M8" s="66" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
       <c r="N8" s="66" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Canal.de.Cor</v>
       </c>
       <c r="O8" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Magenta</v>
+        <f t="shared" si="0"/>
+        <v>Blue</v>
       </c>
       <c r="P8" s="66" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q8" s="66" t="str">
-        <f t="shared" ref="Q8:Q24" si="7">_xlfn.TRANSLATE(P8,"pt","es")</f>
-        <v>Cantidad de color magenta que puede variar entre 0 y 255.</v>
+        <f t="shared" si="3"/>
+        <v>La cantidad de color azul entre eso puede variar de 0 a 255.</v>
       </c>
       <c r="R8" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Cromáticos</v>
+      </c>
+      <c r="T8" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Paletas</v>
+      </c>
+      <c r="U8" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="V8" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-8</v>
+      </c>
+      <c r="X8" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y8" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z8" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA8" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Amount of blue color between that can vary from 0 to 255.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="64">
+        <v>9</v>
+      </c>
+      <c r="B9" s="71" t="s">
+        <v>344</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="74" t="s">
+        <v>327</v>
+      </c>
+      <c r="L9" s="66" t="str">
+        <f t="shared" ref="L9:L11" si="6">_xlfn.CONCAT(C9)</f>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M9" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Paletas</v>
+      </c>
+      <c r="N9" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="O9" s="66" t="str">
+        <f t="shared" si="0"/>
+        <v>Alfa</v>
+      </c>
+      <c r="P9" s="66" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q9" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v>Cantidad de transparencia que puede variar entre 0 y 255.</v>
+      </c>
+      <c r="R9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Cromáticos</v>
+      </c>
+      <c r="T9" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Paletas</v>
+      </c>
+      <c r="U9" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Canal.de.Cor</v>
+      </c>
+      <c r="V9" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="W9" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-9</v>
+      </c>
+      <c r="X9" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y9" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z9" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA9" s="60" t="str">
+        <f t="shared" si="4"/>
+        <v>Amount of transparency that can vary between 0 and 255.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="64">
+        <v>10</v>
+      </c>
+      <c r="B10" s="71" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="75" t="s">
+        <v>315</v>
+      </c>
+      <c r="L10" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T8" s="60" t="str">
-        <f t="shared" si="6"/>
+      <c r="M10" s="67" t="str">
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
-      <c r="U8" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="V8" s="60" t="s">
+      <c r="N10" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>Cor.Digital</v>
+      </c>
+      <c r="O10" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>CMY</v>
+      </c>
+      <c r="P10" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q10" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v>Color digital compuesto por canales CMY.</v>
+      </c>
+      <c r="R10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Cromáticos</v>
+      </c>
+      <c r="T10" s="60" t="str">
+        <f t="shared" si="1"/>
+        <v>Paletas</v>
+      </c>
+      <c r="U10" s="65" t="str">
+        <f t="shared" si="1"/>
+        <v>Cor.Digital</v>
+      </c>
+      <c r="V10" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W8" s="78" t="str">
+      <c r="W10" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-10</v>
+      </c>
+      <c r="X10" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y10" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z10" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA10" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-8</v>
-      </c>
-      <c r="X8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="60" t="str">
-        <f t="shared" ref="AA8:AA24" si="8">_xlfn.TRANSLATE(P8,"pt","en")</f>
-        <v>Amount of magenta color that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="64">
-        <v>9</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="75" t="s">
+        <v>Digital color composed of CMY channels.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="64">
+        <v>11</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>344</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="L9" s="66" t="str">
-        <f>_xlfn.CONCAT(C9)</f>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M9" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
-      </c>
-      <c r="N9" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="O9" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Yellow</v>
-      </c>
-      <c r="P9" s="66" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q9" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>La cantidad de color amarillo entre los cuales puede variar de 0 a 255.</v>
-      </c>
-      <c r="R9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="60" t="str">
+      <c r="E11" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="L11" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T9" s="60" t="str">
-        <f t="shared" si="6"/>
+      <c r="M11" s="67" t="str">
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
-      <c r="U9" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="V9" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W9" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-9</v>
-      </c>
-      <c r="X9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Amount of yellow color between which can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="64">
-        <v>10</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="75" t="s">
-        <v>342</v>
-      </c>
-      <c r="L10" s="66" t="str">
-        <f t="shared" ref="L10:L24" si="9">_xlfn.CONCAT(C10)</f>
+      <c r="N11" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>Cor.Digital</v>
+      </c>
+      <c r="O11" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>CMYB</v>
+      </c>
+      <c r="P11" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q11" s="66" t="str">
+        <f t="shared" si="3"/>
+        <v>Color digital compuesto por canales CMYB.</v>
+      </c>
+      <c r="R11" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="60" t="str">
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="M10" s="66" t="str">
-        <f t="shared" si="5"/>
+      <c r="T11" s="60" t="str">
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="N10" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="O10" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Black</v>
-      </c>
-      <c r="P10" s="66" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q10" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>La cantidad de color negro entre ellos puede variar de 0 a 255.</v>
-      </c>
-      <c r="R10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T10" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
-      </c>
-      <c r="U10" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="V10" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W10" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-10</v>
-      </c>
-      <c r="X10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Amount of black color between which can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="64">
-        <v>11</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="75" t="s">
-        <v>343</v>
-      </c>
-      <c r="L11" s="66" t="str">
-        <f>_xlfn.CONCAT(C11)</f>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M11" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
-      </c>
-      <c r="N11" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="O11" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Red</v>
-      </c>
-      <c r="P11" s="66" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q11" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Cantidad de color rojo que puede variar entre 0 y 255.</v>
-      </c>
-      <c r="R11" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T11" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
-      </c>
       <c r="U11" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
+        <f t="shared" si="1"/>
+        <v>Cor.Digital</v>
       </c>
       <c r="V11" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W11" s="78" t="str">
+      <c r="W11" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-11</v>
+      </c>
+      <c r="X11" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y11" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z11" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA11" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-11</v>
-      </c>
-      <c r="X11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Amount of red color that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Digital color composed of CMYB channels.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="64">
         <v>12</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="74" t="s">
+        <v>346</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K12" s="75" t="s">
-        <v>341</v>
-      </c>
-      <c r="L12" s="66" t="str">
-        <f>_xlfn.CONCAT(C12)</f>
+        <v>313</v>
+      </c>
+      <c r="L12" s="67" t="str">
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
-      <c r="M12" s="66" t="str">
-        <f t="shared" si="5"/>
+      <c r="M12" s="67" t="str">
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
-      <c r="N12" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="O12" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Green</v>
-      </c>
-      <c r="P12" s="66" t="s">
-        <v>243</v>
+      <c r="N12" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>Cor.Digital</v>
+      </c>
+      <c r="O12" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>RGB</v>
+      </c>
+      <c r="P12" s="67" t="s">
+        <v>234</v>
       </c>
       <c r="Q12" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>La cantidad de color verde entre eso puede variar de 0 a 255.</v>
+        <f t="shared" si="3"/>
+        <v>Color digital compuesto por canales RGB.</v>
       </c>
       <c r="R12" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S12" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T12" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U12" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
+        <f t="shared" si="1"/>
+        <v>Cor.Digital</v>
       </c>
       <c r="V12" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W12" s="78" t="str">
+      <c r="W12" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-12</v>
+      </c>
+      <c r="X12" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y12" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z12" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA12" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-12</v>
-      </c>
-      <c r="X12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Amount of green color between that can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Digital color composed of RGB channels.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64">
         <v>13</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="74" t="s">
+        <v>346</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="73" t="s">
         <v>1</v>
       </c>
       <c r="K13" s="75" t="s">
-        <v>347</v>
-      </c>
-      <c r="L13" s="66" t="str">
-        <f>_xlfn.CONCAT(C13)</f>
+        <v>314</v>
+      </c>
+      <c r="L13" s="67" t="str">
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
-      <c r="M13" s="66" t="str">
-        <f t="shared" si="5"/>
+      <c r="M13" s="67" t="str">
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
-      <c r="N13" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="O13" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Blue</v>
-      </c>
-      <c r="P13" s="66" t="s">
-        <v>237</v>
+      <c r="N13" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>Cor.Digital</v>
+      </c>
+      <c r="O13" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>RGBA</v>
+      </c>
+      <c r="P13" s="67" t="s">
+        <v>230</v>
       </c>
       <c r="Q13" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>La cantidad de color azul entre eso puede variar de 0 a 255.</v>
+        <f t="shared" si="3"/>
+        <v>Color digital compuesto por canales RGBA. El Canal A define transparencia.</v>
       </c>
       <c r="R13" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S13" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T13" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U13" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
+        <f t="shared" si="1"/>
+        <v>Cor.Digital</v>
       </c>
       <c r="V13" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W13" s="78" t="str">
+      <c r="W13" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-13</v>
+      </c>
+      <c r="X13" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y13" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z13" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA13" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-13</v>
-      </c>
-      <c r="X13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Amount of blue color between that can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Digital color composed of RGBA channels. Channel A defines transparency.</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64">
         <v>14</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="75" t="s">
-        <v>340</v>
-      </c>
-      <c r="L14" s="66" t="str">
-        <f t="shared" ref="L14:L16" si="10">_xlfn.CONCAT(C14)</f>
+        <v>346</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="67" t="str">
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
-      <c r="M14" s="66" t="str">
-        <f t="shared" si="5"/>
+      <c r="M14" s="67" t="str">
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
-      <c r="N14" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Canal.de.Cor</v>
-      </c>
-      <c r="O14" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Alfa</v>
-      </c>
-      <c r="P14" s="66" t="s">
-        <v>244</v>
+      <c r="N14" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>Munsell</v>
+      </c>
+      <c r="O14" s="67" t="str">
+        <f t="shared" si="0"/>
+        <v>Hue</v>
+      </c>
+      <c r="P14" s="67" t="s">
+        <v>233</v>
       </c>
       <c r="Q14" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Cantidad de transparencia que puede variar entre 0 y 255.</v>
+        <f t="shared" si="3"/>
+        <v>Sistema de color Munsell: Parámetro de tono.</v>
       </c>
       <c r="R14" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T14" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U14" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Canal.de.Cor</v>
+        <f t="shared" si="1"/>
+        <v>Munsell</v>
       </c>
       <c r="V14" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W14" s="78" t="str">
+      <c r="W14" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-14</v>
+      </c>
+      <c r="X14" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y14" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z14" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA14" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-14</v>
-      </c>
-      <c r="X14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Amount of transparency that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Munsell Color System: Hue Parameter.</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64">
         <v>15</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="G15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="76" t="s">
-        <v>328</v>
+        <v>175</v>
+      </c>
+      <c r="G15" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="73" t="s">
+        <v>1</v>
       </c>
       <c r="L15" s="67" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
       <c r="M15" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
       <c r="N15" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="0"/>
+        <v>Munsell</v>
       </c>
       <c r="O15" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>CMY</v>
+        <f t="shared" si="0"/>
+        <v>Luminosidade</v>
       </c>
       <c r="P15" s="67" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="Q15" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Color digital compuesto por canales CMY.</v>
+        <f t="shared" si="3"/>
+        <v>Sistema de color Munsell: Parámetro de luminosidad.</v>
       </c>
       <c r="R15" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T15" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U15" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="1"/>
+        <v>Munsell</v>
       </c>
       <c r="V15" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W15" s="78" t="str">
+      <c r="W15" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-15</v>
+      </c>
+      <c r="X15" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y15" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z15" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA15" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-15</v>
-      </c>
-      <c r="X15" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Digital color composed of CMY channels.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Munsell color system: Luminosity parameter.</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64">
         <v>16</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="G16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="76" t="s">
-        <v>329</v>
+        <v>176</v>
+      </c>
+      <c r="G16" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="73" t="s">
+        <v>1</v>
       </c>
       <c r="L16" s="67" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
       <c r="M16" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
       <c r="N16" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="0"/>
+        <v>Munsell</v>
       </c>
       <c r="O16" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>CMYB</v>
+        <f t="shared" si="0"/>
+        <v>Croma</v>
       </c>
       <c r="P16" s="67" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="Q16" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Color digital compuesto por canales CMYB.</v>
+        <f t="shared" si="3"/>
+        <v>Sistema de color Munsell: Parámetro Croma. Es el grado de distancia de un color al color neutro del mismo valor. Un cromo bajo debilita el color. Un alto nivel de cromancia para colores saturados, intensos o vivos.</v>
       </c>
       <c r="R16" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T16" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U16" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="1"/>
+        <v>Munsell</v>
       </c>
       <c r="V16" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W16" s="78" t="str">
+      <c r="W16" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-16</v>
+      </c>
+      <c r="X16" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y16" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z16" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA16" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-16</v>
-      </c>
-      <c r="X16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Digital color composed of CMYB channels.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Munsell Color System: Croma Parameter. It is the degree of distance of a color from the neutral color of the same value. A low chroma weakens the color. A high chroma for saturated, strong, or vivid color.</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64">
         <v>17</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="76" t="s">
-        <v>326</v>
+        <v>227</v>
+      </c>
+      <c r="G17" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="73" t="s">
+        <v>1</v>
       </c>
       <c r="L17" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
       <c r="M17" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Paletas</v>
       </c>
       <c r="N17" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="0"/>
+        <v>Munsell</v>
       </c>
       <c r="O17" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>RGB</v>
+        <f t="shared" si="0"/>
+        <v>Cor.Munsell</v>
       </c>
       <c r="P17" s="67" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="Q17" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Color digital compuesto por canales RGB.</v>
+        <f t="shared" si="3"/>
+        <v>Color específico del sistema Munsell.</v>
       </c>
       <c r="R17" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
       <c r="T17" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
       <c r="U17" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="1"/>
+        <v>Munsell</v>
       </c>
       <c r="V17" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W17" s="78" t="str">
+      <c r="W17" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-17</v>
+      </c>
+      <c r="X17" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y17" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z17" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA17" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-17</v>
-      </c>
-      <c r="X17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Digital color composed of RGB channels.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Munsell system-specific color.</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64">
         <v>18</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>361</v>
+        <v>345</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>119</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="76" t="s">
-        <v>327</v>
+        <v>115</v>
+      </c>
+      <c r="G18" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="73" t="s">
+        <v>1</v>
       </c>
       <c r="L18" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
       <c r="M18" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
+        <f t="shared" ref="M18:O19" si="7">_xlfn.CONCAT("", D18)</f>
+        <v>Catálogo</v>
       </c>
       <c r="N18" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="7"/>
+        <v>Pantone</v>
       </c>
       <c r="O18" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>RGBA</v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Cor.Pantone </v>
       </c>
       <c r="P18" s="67" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q18" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Color digital compuesto por canales RGBA. El canal A define transparencia.</v>
+        <f t="shared" si="3"/>
+        <v>Color específico del catálogo de Pantone.</v>
       </c>
       <c r="R18" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="S18:U19" si="8">SUBSTITUTE(C18, "_", " ")</f>
         <v>Cromáticos</v>
       </c>
       <c r="T18" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
+        <f t="shared" si="8"/>
+        <v>Catálogo</v>
       </c>
       <c r="U18" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Cor.Digital</v>
+        <f t="shared" si="8"/>
+        <v>Pantone</v>
       </c>
       <c r="V18" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W18" s="78" t="str">
+      <c r="W18" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-18</v>
+      </c>
+      <c r="X18" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y18" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z18" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA18" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-18</v>
-      </c>
-      <c r="X18" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Digital color composed of RGBA channels. Channel A defines transparency.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Specific color from the Pantone catalog.</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64">
         <v>19</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>361</v>
+        <v>345</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>119</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="G19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="73" t="s">
         <v>1</v>
       </c>
       <c r="L19" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>Cromáticos</v>
       </c>
       <c r="M19" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
+        <f t="shared" si="7"/>
+        <v>Catálogo</v>
       </c>
       <c r="N19" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Munsell</v>
+        <f t="shared" si="7"/>
+        <v>DNIT</v>
       </c>
       <c r="O19" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Hue</v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Cor.Dnit </v>
       </c>
       <c r="P19" s="67" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="Q19" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistema de color Munsell: Parámetro de tono.</v>
+        <f t="shared" si="3"/>
+        <v>Colores del catálogo del Departamento Nacional de Infraestructuras de Transporte de Brasil.</v>
       </c>
       <c r="R19" s="65" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="60" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Cromáticos</v>
       </c>
       <c r="T19" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
+        <f t="shared" si="8"/>
+        <v>Catálogo</v>
       </c>
       <c r="U19" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Munsell</v>
+        <f t="shared" si="8"/>
+        <v>DNIT</v>
       </c>
       <c r="V19" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W19" s="78" t="str">
+      <c r="W19" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-19</v>
+      </c>
+      <c r="X19" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y19" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z19" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA19" s="60" t="str">
         <f t="shared" si="4"/>
-        <v>Key-CROMA-19</v>
-      </c>
-      <c r="X19" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Munsell Color System: Hue Parameter.</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="64">
-        <v>20</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M20" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
-      </c>
-      <c r="N20" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Munsell</v>
-      </c>
-      <c r="O20" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Luminosidade</v>
-      </c>
-      <c r="P20" s="67" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q20" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistema de color Munsell: Parámetro de luminosidad.</v>
-      </c>
-      <c r="R20" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T20" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
-      </c>
-      <c r="U20" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Munsell</v>
-      </c>
-      <c r="V20" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W20" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-20</v>
-      </c>
-      <c r="X20" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Munsell color system: Luminosity parameter.</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="64">
-        <v>21</v>
-      </c>
-      <c r="B21" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E21" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="G21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M21" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
-      </c>
-      <c r="N21" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Munsell</v>
-      </c>
-      <c r="O21" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Croma</v>
-      </c>
-      <c r="P21" s="67" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q21" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistema de color Munsell: Cromina de parámetros. Es el grado de distancia de un color al color neutro del mismo valor. Una cromina baja debilita el color. Una cromancia alta para color saturado, intenso o vivo.</v>
-      </c>
-      <c r="R21" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T21" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
-      </c>
-      <c r="U21" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Munsell</v>
-      </c>
-      <c r="V21" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W21" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-21</v>
-      </c>
-      <c r="X21" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Munsell Color System: Parameter Chroma. It is the degree of distance of a color from the neutral color of the same value. A low chroma weakens the color. A high chroma for saturated, strong, or vivid color.</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="64">
-        <v>22</v>
-      </c>
-      <c r="B22" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="E22" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="G22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M22" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Paletas</v>
-      </c>
-      <c r="N22" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Munsell</v>
-      </c>
-      <c r="O22" s="67" t="str">
-        <f t="shared" si="5"/>
-        <v>Cor.Munsell</v>
-      </c>
-      <c r="P22" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q22" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Color específico del sistema Munsell.</v>
-      </c>
-      <c r="R22" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T22" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Paletas</v>
-      </c>
-      <c r="U22" s="65" t="str">
-        <f t="shared" si="6"/>
-        <v>Munsell</v>
-      </c>
-      <c r="V22" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W22" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-22</v>
-      </c>
-      <c r="X22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Munsell system-specific color.</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="64">
-        <v>23</v>
-      </c>
-      <c r="B23" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M23" s="67" t="str">
-        <f t="shared" ref="M23:O24" si="11">_xlfn.CONCAT("", D23)</f>
-        <v>Catálogo</v>
-      </c>
-      <c r="N23" s="67" t="str">
-        <f t="shared" si="11"/>
-        <v>Pantone</v>
-      </c>
-      <c r="O23" s="67" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">Cor.Pantone </v>
-      </c>
-      <c r="P23" s="67" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q23" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Color específico del catálogo de Pantone.</v>
-      </c>
-      <c r="R23" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S23" s="60" t="str">
-        <f t="shared" ref="S23:U24" si="12">SUBSTITUTE(C23, "_", " ")</f>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T23" s="60" t="str">
-        <f t="shared" si="12"/>
-        <v>Catálogo</v>
-      </c>
-      <c r="U23" s="65" t="str">
-        <f t="shared" si="12"/>
-        <v>Pantone</v>
-      </c>
-      <c r="V23" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W23" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-23</v>
-      </c>
-      <c r="X23" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="60" t="str">
-        <f t="shared" si="8"/>
-        <v>Specific color from the Pantone catalog.</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="64">
-        <v>24</v>
-      </c>
-      <c r="B24" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M24" s="67" t="str">
-        <f t="shared" si="11"/>
-        <v>Catálogo</v>
-      </c>
-      <c r="N24" s="67" t="str">
-        <f t="shared" si="11"/>
-        <v>DNIT</v>
-      </c>
-      <c r="O24" s="67" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">Cor.Dnit </v>
-      </c>
-      <c r="P24" s="67" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q24" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Colores del catálogo del Departamento Nacional de Infraestructuras de Transporte de Brasil.</v>
-      </c>
-      <c r="R24" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="60" t="str">
-        <f t="shared" si="12"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="T24" s="60" t="str">
-        <f t="shared" si="12"/>
-        <v>Catálogo</v>
-      </c>
-      <c r="U24" s="65" t="str">
-        <f t="shared" si="12"/>
-        <v>DNIT</v>
-      </c>
-      <c r="V24" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="W24" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-CROMA-24</v>
-      </c>
-      <c r="X24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="60" t="str">
-        <f t="shared" si="8"/>
         <v>Colors from the catalog of the National Department of Transport Infrastructure of Brazil.</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B24">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19 A2:B19">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:J1 C7:F24 S1:Z1 V2:V6 L7:Q24 S7:V24">
-    <cfRule type="cellIs" dxfId="16" priority="22" operator="equal">
+  <conditionalFormatting sqref="A1:J1 C2:F19 S1:Z1 L2:Q19 S2:V19">
+    <cfRule type="cellIs" dxfId="11" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1:Q1 K7:K18">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA24">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+  <conditionalFormatting sqref="K1:Q1 K2:K13">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6022,16 +5458,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="39" t="s">
         <v>22</v>
       </c>
@@ -6096,7 +5532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="39">
         <v>2</v>
       </c>
@@ -6158,71 +5594,6 @@
         <v>1</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6241,14 +5612,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="36">
         <v>1</v>
       </c>
@@ -6259,7 +5630,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -6283,33 +5654,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.15234375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.15234375" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.69140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.3828125" style="42" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.15234375" style="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.3828125" style="42" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.15234375" style="42" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.84375" style="42" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.3046875" style="42" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="91.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.85546875" style="42" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="91.42578125" style="42" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5" style="42" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.15234375" style="42" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>91</v>
       </c>
@@ -6380,7 +5751,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -6400,13 +5771,13 @@
         <v>122</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="J2" s="57" t="s">
         <v>1</v>
@@ -6421,7 +5792,7 @@
         <v>260</v>
       </c>
       <c r="N2" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O2" s="47">
         <v>255</v>
@@ -6452,7 +5823,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
         <v>3</v>
       </c>
@@ -6472,13 +5843,13 @@
         <v>122</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="J3" s="57" t="s">
         <v>1</v>
@@ -6493,7 +5864,7 @@
         <v>261</v>
       </c>
       <c r="N3" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="O3" s="47">
         <v>255</v>
@@ -6524,7 +5895,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -6544,13 +5915,13 @@
         <v>122</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>1</v>
@@ -6565,7 +5936,7 @@
         <v>262</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="O4" s="47">
         <v>255</v>
@@ -6596,7 +5967,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>5</v>
       </c>
@@ -6622,7 +5993,7 @@
         <v>122</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="J5" s="57" t="s">
         <v>1</v>
@@ -6637,7 +6008,7 @@
         <v>263</v>
       </c>
       <c r="N5" s="45" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="O5" s="47">
         <v>255</v>
@@ -6668,7 +6039,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -6688,7 +6059,7 @@
         <v>122</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H6" s="57" t="s">
         <v>1</v>
@@ -6706,22 +6077,22 @@
         <v>140</v>
       </c>
       <c r="M6" s="47" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="N6" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O6" s="47">
         <v>255</v>
       </c>
       <c r="P6" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q6" s="47">
         <v>0</v>
       </c>
       <c r="R6" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S6" s="47">
         <v>0</v>
@@ -6733,14 +6104,14 @@
         <v>1</v>
       </c>
       <c r="V6" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W6" s="47" t="str">
         <f t="shared" ref="W6:W10" si="1">IF(OR(V6="cor.rgb",V6="cor.cmy",V6="cor.rgba",V6="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O6,".",Q6,".",S6,".",U6,""""), ".null",""), V6)</f>
         <v>"255.0.0"</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -6760,7 +6131,7 @@
         <v>122</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H7" s="57" t="s">
         <v>1</v>
@@ -6778,22 +6149,22 @@
         <v>140</v>
       </c>
       <c r="M7" s="47" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="N7" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O7" s="47">
         <v>0</v>
       </c>
       <c r="P7" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q7" s="47">
         <v>255</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S7" s="47">
         <v>0</v>
@@ -6805,14 +6176,14 @@
         <v>1</v>
       </c>
       <c r="V7" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W7" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"0.255.0"</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -6832,7 +6203,7 @@
         <v>122</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H8" s="57" t="s">
         <v>1</v>
@@ -6850,22 +6221,22 @@
         <v>140</v>
       </c>
       <c r="M8" s="47" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="N8" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O8" s="47">
         <v>0</v>
       </c>
       <c r="P8" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q8" s="47">
         <v>0</v>
       </c>
       <c r="R8" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S8" s="47">
         <v>255</v>
@@ -6877,14 +6248,14 @@
         <v>1</v>
       </c>
       <c r="V8" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W8" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"0.0.255"</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -6904,7 +6275,7 @@
         <v>122</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H9" s="57" t="s">
         <v>1</v>
@@ -6922,22 +6293,22 @@
         <v>140</v>
       </c>
       <c r="M9" s="47" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N9" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O9" s="47">
         <v>200</v>
       </c>
       <c r="P9" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q9" s="47">
         <v>200</v>
       </c>
       <c r="R9" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S9" s="47">
         <v>200</v>
@@ -6949,14 +6320,14 @@
         <v>1</v>
       </c>
       <c r="V9" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W9" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"200.200.200"</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -6976,7 +6347,7 @@
         <v>122</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H10" s="57" t="s">
         <v>1</v>
@@ -6994,22 +6365,22 @@
         <v>140</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="N10" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O10" s="47">
         <v>120</v>
       </c>
       <c r="P10" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q10" s="47">
         <v>120</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S10" s="47">
         <v>120</v>
@@ -7021,14 +6392,14 @@
         <v>1</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W10" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"120.120.120"</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -7048,7 +6419,7 @@
         <v>122</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H11" s="57" t="s">
         <v>1</v>
@@ -7066,22 +6437,22 @@
         <v>140</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O11" s="47">
         <v>20</v>
       </c>
       <c r="P11" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q11" s="47">
         <v>20</v>
       </c>
       <c r="R11" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S11" s="47">
         <v>20</v>
@@ -7093,14 +6464,14 @@
         <v>1</v>
       </c>
       <c r="V11" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W11" s="47" t="str">
         <f>IF(OR(V11="cor.rgb",V11="cor.cmy",V11="cor.rgba",V11="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O11,".",Q11,".",S11,".",U11,""""), ".null",""), V11)</f>
         <v>"20.20.20"</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -7120,7 +6491,7 @@
         <v>122</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H12" s="57" t="s">
         <v>1</v>
@@ -7138,22 +6509,22 @@
         <v>140</v>
       </c>
       <c r="M12" s="47" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="N12" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O12" s="47">
         <v>150</v>
       </c>
       <c r="P12" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q12" s="47">
         <v>30</v>
       </c>
       <c r="R12" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S12" s="47">
         <v>10</v>
@@ -7165,14 +6536,14 @@
         <v>1</v>
       </c>
       <c r="V12" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W12" s="47" t="str">
         <f>IF(OR(V12="cor.rgb",V12="cor.cmy",V12="cor.rgba",V12="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O12,".",Q12,".",S12,".",U12,""""), ".null",""), V12)</f>
         <v>"150.30.10"</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -7192,7 +6563,7 @@
         <v>122</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H13" s="57" t="s">
         <v>1</v>
@@ -7210,22 +6581,22 @@
         <v>140</v>
       </c>
       <c r="M13" s="47" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="N13" s="45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O13" s="47">
         <v>150</v>
       </c>
       <c r="P13" s="45" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Q13" s="47">
         <v>40</v>
       </c>
       <c r="R13" s="44" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="S13" s="47">
         <v>10</v>
@@ -7237,14 +6608,14 @@
         <v>1</v>
       </c>
       <c r="V13" s="44" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W13" s="47" t="str">
         <f t="shared" ref="W13:W15" si="2">IF(OR(V13="cor.rgb",V13="cor.cmy",V13="cor.rgba",V13="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O13,".",Q13,".",S13,".",U13,""""), ".null",""), V13)</f>
         <v>"150.40.10"</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -7264,7 +6635,7 @@
         <v>122</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="H14" s="57" t="s">
         <v>1</v>
@@ -7282,22 +6653,22 @@
         <v>140</v>
       </c>
       <c r="M14" s="47" t="s">
+        <v>326</v>
+      </c>
+      <c r="N14" s="45" t="s">
         <v>339</v>
-      </c>
-      <c r="N14" s="45" t="s">
-        <v>352</v>
       </c>
       <c r="O14" s="47">
         <v>150</v>
       </c>
       <c r="P14" s="45" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q14" s="47">
         <v>50</v>
       </c>
       <c r="R14" s="44" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="S14" s="47">
         <v>10</v>
@@ -7309,14 +6680,14 @@
         <v>1</v>
       </c>
       <c r="V14" s="44" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W14" s="47" t="str">
         <f t="shared" si="2"/>
         <v>"150.50.10"</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -7336,7 +6707,7 @@
         <v>122</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="H15" s="57" t="s">
         <v>1</v>
@@ -7354,22 +6725,22 @@
         <v>140</v>
       </c>
       <c r="M15" s="47" t="s">
+        <v>326</v>
+      </c>
+      <c r="N15" s="45" t="s">
         <v>339</v>
-      </c>
-      <c r="N15" s="45" t="s">
-        <v>352</v>
       </c>
       <c r="O15" s="47">
         <v>150</v>
       </c>
       <c r="P15" s="45" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q15" s="47">
         <v>60</v>
       </c>
       <c r="R15" s="44" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="S15" s="47">
         <v>10</v>
@@ -7381,14 +6752,14 @@
         <v>1</v>
       </c>
       <c r="V15" s="44" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W15" s="47" t="str">
         <f t="shared" si="2"/>
         <v>"150.60.10"</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -7460,7 +6831,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -7498,7 +6869,7 @@
         <v>140</v>
       </c>
       <c r="M17" s="47" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="N17" s="44" t="s">
         <v>133</v>
@@ -7532,12 +6903,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>18</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>130</v>
@@ -7570,7 +6941,7 @@
         <v>140</v>
       </c>
       <c r="M18" s="47" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="N18" s="52" t="s">
         <v>1</v>
@@ -7604,12 +6975,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="31">
         <v>19</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>128</v>
@@ -7642,7 +7013,7 @@
         <v>140</v>
       </c>
       <c r="M19" s="47" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="N19" s="52" t="s">
         <v>1</v>
@@ -7676,12 +7047,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="31">
         <v>20</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>129</v>
@@ -7714,7 +7085,7 @@
         <v>140</v>
       </c>
       <c r="M20" s="47" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="N20" s="52" t="s">
         <v>1</v>
@@ -7748,12 +7119,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="31">
         <v>21</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>127</v>
@@ -7786,7 +7157,7 @@
         <v>140</v>
       </c>
       <c r="M21" s="47" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="N21" s="52" t="s">
         <v>1</v>
@@ -7820,7 +7191,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -7858,22 +7229,22 @@
         <v>140</v>
       </c>
       <c r="M22" s="47" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="N22" s="45" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O22" s="47">
         <v>0</v>
       </c>
       <c r="P22" s="45" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q22" s="47">
         <v>0</v>
       </c>
       <c r="R22" s="44" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="S22" s="47">
         <v>100</v>
@@ -7885,14 +7256,14 @@
         <v>1</v>
       </c>
       <c r="V22" s="44" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W22" s="47" t="str">
         <f t="shared" ref="W22:W24" si="3">IF(OR(V22="cor.rgb",V22="cor.cmy",V22="cor.rgba",V22="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O22,".",Q22,".",S22,".",U22,""""), ".null",""), V22)</f>
         <v>"0.0.100"</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -7930,22 +7301,22 @@
         <v>140</v>
       </c>
       <c r="M23" s="47" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="N23" s="45" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O23" s="47">
         <v>63</v>
       </c>
       <c r="P23" s="45" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q23" s="47">
         <v>23</v>
       </c>
       <c r="R23" s="44" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="S23" s="47">
         <v>100</v>
@@ -7957,14 +7328,14 @@
         <v>1</v>
       </c>
       <c r="V23" s="44" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W23" s="47" t="str">
         <f t="shared" si="3"/>
         <v>"63.23.100"</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -8002,22 +7373,22 @@
         <v>140</v>
       </c>
       <c r="M24" s="47" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="N24" s="45" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O24" s="47">
         <v>100</v>
       </c>
       <c r="P24" s="45" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q24" s="47">
         <v>0</v>
       </c>
       <c r="R24" s="44" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="S24" s="47">
         <v>100</v>
@@ -8029,14 +7400,14 @@
         <v>1</v>
       </c>
       <c r="V24" s="44" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W24" s="47" t="str">
         <f t="shared" si="3"/>
         <v>"100.0.100"</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -8107,7 +7478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -8145,7 +7516,7 @@
         <v>140</v>
       </c>
       <c r="M26" s="47" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="N26" s="52" t="s">
         <v>1</v>
@@ -8178,7 +7549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -8216,7 +7587,7 @@
         <v>140</v>
       </c>
       <c r="M27" s="47" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="N27" s="52" t="s">
         <v>1</v>
@@ -8249,7 +7620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -8287,7 +7658,7 @@
         <v>140</v>
       </c>
       <c r="M28" s="47" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="N28" s="52" t="s">
         <v>1</v>
@@ -8320,7 +7691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -8358,7 +7729,7 @@
         <v>140</v>
       </c>
       <c r="M29" s="47" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="N29" s="52" t="s">
         <v>1</v>
@@ -8391,7 +7762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -8429,7 +7800,7 @@
         <v>140</v>
       </c>
       <c r="M30" s="47" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="N30" s="52" t="s">
         <v>1</v>
@@ -8462,7 +7833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -8500,7 +7871,7 @@
         <v>140</v>
       </c>
       <c r="M31" s="47" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="N31" s="52" t="s">
         <v>1</v>
@@ -8533,7 +7904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -8571,7 +7942,7 @@
         <v>140</v>
       </c>
       <c r="M32" s="47" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="N32" s="52" t="s">
         <v>1</v>
@@ -8604,7 +7975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -8642,7 +8013,7 @@
         <v>140</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="N33" s="52" t="s">
         <v>1</v>
@@ -8675,7 +8046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -8713,7 +8084,7 @@
         <v>140</v>
       </c>
       <c r="M34" s="47" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="N34" s="52" t="s">
         <v>1</v>
@@ -8746,7 +8117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -8784,7 +8155,7 @@
         <v>140</v>
       </c>
       <c r="M35" s="47" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="N35" s="52" t="s">
         <v>1</v>
@@ -8817,7 +8188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -8888,7 +8259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -8926,7 +8297,7 @@
         <v>140</v>
       </c>
       <c r="M37" s="47" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="N37" s="52" t="s">
         <v>1</v>
@@ -8959,7 +8330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -8997,7 +8368,7 @@
         <v>140</v>
       </c>
       <c r="M38" s="47" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="N38" s="52" t="s">
         <v>1</v>
@@ -9030,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -9068,7 +8439,7 @@
         <v>140</v>
       </c>
       <c r="M39" s="47" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="N39" s="52" t="s">
         <v>1</v>
@@ -9101,7 +8472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <v>40</v>
       </c>
@@ -9139,7 +8510,7 @@
         <v>140</v>
       </c>
       <c r="M40" s="47" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="N40" s="52" t="s">
         <v>1</v>
@@ -9172,7 +8543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31">
         <v>41</v>
       </c>
@@ -9210,7 +8581,7 @@
         <v>140</v>
       </c>
       <c r="M41" s="47" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="N41" s="52" t="s">
         <v>1</v>
@@ -9243,7 +8614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31">
         <v>42</v>
       </c>
@@ -9281,7 +8652,7 @@
         <v>140</v>
       </c>
       <c r="M42" s="47" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="N42" s="52" t="s">
         <v>1</v>
@@ -9314,7 +8685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="31">
         <v>43</v>
       </c>
@@ -9352,7 +8723,7 @@
         <v>140</v>
       </c>
       <c r="M43" s="47" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="N43" s="52" t="s">
         <v>1</v>
@@ -9385,7 +8756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="31">
         <v>44</v>
       </c>
@@ -9423,7 +8794,7 @@
         <v>140</v>
       </c>
       <c r="M44" s="47" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="N44" s="52" t="s">
         <v>1</v>
@@ -9456,7 +8827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="31">
         <v>45</v>
       </c>
@@ -9494,7 +8865,7 @@
         <v>140</v>
       </c>
       <c r="M45" s="47" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="N45" s="52" t="s">
         <v>1</v>
@@ -9527,7 +8898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="31">
         <v>46</v>
       </c>
@@ -9565,7 +8936,7 @@
         <v>140</v>
       </c>
       <c r="M46" s="47" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="N46" s="52" t="s">
         <v>1</v>
@@ -9598,7 +8969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="31">
         <v>47</v>
       </c>
@@ -9636,7 +9007,7 @@
         <v>140</v>
       </c>
       <c r="M47" s="47" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N47" s="52" t="s">
         <v>1</v>
@@ -9669,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="31">
         <v>48</v>
       </c>
@@ -9707,7 +9078,7 @@
         <v>140</v>
       </c>
       <c r="M48" s="47" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="N48" s="52" t="s">
         <v>1</v>
@@ -9740,7 +9111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31">
         <v>49</v>
       </c>
@@ -9778,7 +9149,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="47" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="N49" s="52" t="s">
         <v>1</v>
@@ -9811,7 +9182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -9849,7 +9220,7 @@
         <v>140</v>
       </c>
       <c r="M50" s="47" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="N50" s="52" t="s">
         <v>1</v>
@@ -9882,7 +9253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -9920,7 +9291,7 @@
         <v>140</v>
       </c>
       <c r="M51" s="47" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="N51" s="52" t="s">
         <v>1</v>
@@ -9953,7 +9324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -9991,7 +9362,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="55" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="N52" s="54" t="s">
         <v>182</v>
@@ -10024,7 +9395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -10062,7 +9433,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="55" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="N53" s="54" t="s">
         <v>182</v>
@@ -10095,7 +9466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -10133,7 +9504,7 @@
         <v>140</v>
       </c>
       <c r="M54" s="55" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="N54" s="54" t="s">
         <v>182</v>
@@ -10166,7 +9537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -10237,7 +9608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -10308,7 +9679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -10379,7 +9750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -10450,7 +9821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -10521,7 +9892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -10592,7 +9963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -10663,7 +10034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -10770,15 +10141,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.3046875" customWidth="1"/>
-    <col min="4" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -10789,7 +10160,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -10800,7 +10171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -10811,7 +10182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -10822,7 +10193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -10833,7 +10204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -10844,7 +10215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -10852,10 +10223,10 @@
         <v>28</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -10863,10 +10234,10 @@
         <v>37</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -10874,10 +10245,10 @@
         <v>36</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -10885,10 +10256,10 @@
         <v>35</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -10896,10 +10267,10 @@
         <v>34</v>
       </c>
       <c r="C11" s="69" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -10907,10 +10278,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="69" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -10918,10 +10289,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="69" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -10929,10 +10300,10 @@
         <v>31</v>
       </c>
       <c r="C14" s="69" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -10940,50 +10311,50 @@
         <v>30</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C16" s="29" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C17" s="29" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C18" s="29" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C19" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C20" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C21" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C22" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C23" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C24" s="68" t="s">
         <v>1</v>
       </c>
